--- a/excel/Scramble Rima.xlsx
+++ b/excel/Scramble Rima.xlsx
@@ -8,26 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.08.08\Scramble\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A93A0626-5D33-4C9A-B0A5-F271A001999A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58445338-A6D7-4F26-92C0-17E4E6E2AEC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
     <sheet name="Pinigai" sheetId="15" r:id="rId2"/>
-    <sheet name="August 2026" sheetId="36" r:id="rId3"/>
-    <sheet name="July 2026" sheetId="35" r:id="rId4"/>
-    <sheet name="June 2026" sheetId="34" r:id="rId5"/>
-    <sheet name="May 2026" sheetId="33" r:id="rId6"/>
-    <sheet name="April 2026" sheetId="32" r:id="rId7"/>
-    <sheet name="March 2026" sheetId="31" r:id="rId8"/>
-    <sheet name="February 2026" sheetId="30" r:id="rId9"/>
-    <sheet name="January 2026" sheetId="29" r:id="rId10"/>
-    <sheet name="December 2025" sheetId="28" r:id="rId11"/>
-    <sheet name="November 2025" sheetId="27" r:id="rId12"/>
-    <sheet name="October 2025" sheetId="26" r:id="rId13"/>
-    <sheet name="September 2025" sheetId="25" r:id="rId14"/>
-    <sheet name="August 2025" sheetId="14" r:id="rId15"/>
+    <sheet name="September 2026" sheetId="37" r:id="rId3"/>
+    <sheet name="August 2026" sheetId="36" r:id="rId4"/>
+    <sheet name="July 2026" sheetId="35" r:id="rId5"/>
+    <sheet name="June 2026" sheetId="34" r:id="rId6"/>
+    <sheet name="May 2026" sheetId="33" r:id="rId7"/>
+    <sheet name="April 2026" sheetId="32" r:id="rId8"/>
+    <sheet name="March 2026" sheetId="31" r:id="rId9"/>
+    <sheet name="February 2026" sheetId="30" r:id="rId10"/>
+    <sheet name="January 2026" sheetId="29" r:id="rId11"/>
+    <sheet name="December 2025" sheetId="28" r:id="rId12"/>
+    <sheet name="November 2025" sheetId="27" r:id="rId13"/>
+    <sheet name="October 2025" sheetId="26" r:id="rId14"/>
+    <sheet name="September 2025" sheetId="25" r:id="rId15"/>
+    <sheet name="August 2025" sheetId="14" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -50,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="60">
   <si>
     <t>Paskola</t>
   </si>
@@ -228,6 +229,9 @@
   <si>
     <t>August 2026</t>
   </si>
+  <si>
+    <t>September 2026</t>
+  </si>
 </sst>
 </file>
 
@@ -370,7 +374,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -459,6 +463,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -485,7 +495,35 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="56">
+  <dxfs count="60">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -912,7 +950,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C92B417E-0E73-40BA-95CB-0B8A5F160456}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C5B9A1C-BE8D-4AA8-B425-A2B3857AC890}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -968,7 +1006,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B495DA4-2D50-43E7-92C9-52E679196A7D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78E2DBBC-C5B2-4288-AC0A-95368A14A86A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1024,7 +1062,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67D9ED54-8C5F-4763-A103-EA86015ECDEF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B495DA4-2D50-43E7-92C9-52E679196A7D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1080,6 +1118,62 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67D9ED54-8C5F-4763-A103-EA86015ECDEF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3619500"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>914400</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD13F6DB-3617-4E16-85C6-CE67C2928B61}"/>
             </a:ext>
           </a:extLst>
@@ -1115,7 +1209,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1192,7 +1286,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D26DB4C-231C-4C87-87A9-E78886E7807B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C92B417E-0E73-40BA-95CB-0B8A5F160456}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1248,7 +1342,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13F58B75-E6DB-4D82-A45E-AB511FF3C881}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D26DB4C-231C-4C87-87A9-E78886E7807B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1304,7 +1398,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75ADCD55-EE0C-46E9-9BA6-6DDCE4741191}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13F58B75-E6DB-4D82-A45E-AB511FF3C881}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1360,7 +1454,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4516F9B9-44DD-4606-BEE5-CB1D2AAA0AF1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75ADCD55-EE0C-46E9-9BA6-6DDCE4741191}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1416,7 +1510,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2810C3BC-F093-4506-BBA0-6D497E73A3C1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4516F9B9-44DD-4606-BEE5-CB1D2AAA0AF1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1472,7 +1566,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D2C6C96-E314-400B-9CB5-8B0597A3C6F1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2810C3BC-F093-4506-BBA0-6D497E73A3C1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1528,7 +1622,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BB14DA99-6B92-49A0-A498-AA9896FB5940}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D2C6C96-E314-400B-9CB5-8B0597A3C6F1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1584,7 +1678,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78E2DBBC-C5B2-4288-AC0A-95368A14A86A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BB14DA99-6B92-49A0-A498-AA9896FB5940}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1900,43 +1994,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="34" t="s">
+      <c r="A1" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="36"/>
-      <c r="M1" s="37" t="s">
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="N1" s="37"/>
-      <c r="O1" s="37"/>
-      <c r="Q1" s="38" t="s">
+      <c r="N1" s="39"/>
+      <c r="O1" s="39"/>
+      <c r="Q1" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="R1" s="39"/>
-      <c r="S1" s="39"/>
-      <c r="T1" s="40"/>
-      <c r="U1" s="38" t="s">
+      <c r="R1" s="41"/>
+      <c r="S1" s="41"/>
+      <c r="T1" s="42"/>
+      <c r="U1" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="40"/>
-      <c r="W1" s="34" t="s">
+      <c r="V1" s="42"/>
+      <c r="W1" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="X1" s="35"/>
-      <c r="Y1" s="35"/>
-      <c r="Z1" s="36"/>
+      <c r="X1" s="37"/>
+      <c r="Y1" s="37"/>
+      <c r="Z1" s="38"/>
       <c r="AA1" s="4" t="s">
         <v>27</v>
       </c>
@@ -2092,7 +2186,7 @@
       </c>
       <c r="R3" s="28">
         <f>SUM(H3:H98)-U3</f>
-        <v>678.45999999999958</v>
+        <v>687.56999999999971</v>
       </c>
       <c r="S3" s="27">
         <f>Pinigai!H2</f>
@@ -2100,31 +2194,31 @@
       </c>
       <c r="T3" s="27">
         <f>W3-R3</f>
-        <v>3.0000000000427463E-2</v>
+        <v>2.0000000000322871E-2</v>
       </c>
       <c r="U3" s="28">
         <f>SUM(M3:M98)</f>
-        <v>1102.7800000000002</v>
+        <v>1291.17</v>
       </c>
       <c r="V3" s="28">
         <f>SUM(N3:N98)-AA3</f>
-        <v>44.49</v>
+        <v>53.589999999999996</v>
       </c>
       <c r="W3" s="27">
         <f>Q3+S3+V3</f>
-        <v>678.49</v>
+        <v>687.59</v>
       </c>
       <c r="X3" s="27">
         <f>W3-Q3</f>
-        <v>68.490000000000009</v>
+        <v>77.590000000000032</v>
       </c>
       <c r="Y3" s="29">
         <f>(W3-Q3)/Q3</f>
-        <v>0.11227868852459018</v>
+        <v>0.12719672131147547</v>
       </c>
       <c r="Z3" s="30">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>0.11268935799598695</v>
+        <v>0.11770399212837221</v>
       </c>
       <c r="AA3" s="27">
         <f>SUM(O3:O98)</f>
@@ -2463,7 +2557,7 @@
       </c>
       <c r="N8" s="3">
         <f>'January 2026'!L3</f>
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="O8" s="3">
         <f>'January 2026'!M3</f>
@@ -2563,7 +2657,7 @@
       </c>
       <c r="F10" s="2" t="str">
         <f>'March 2026'!B8</f>
-        <v>0 m. 6 mėn. 0 d.</v>
+        <v>0 m. 6 mėn. 2 d.</v>
       </c>
       <c r="G10" s="7" t="str">
         <f>'March 2026'!B15</f>
@@ -2575,15 +2669,15 @@
       </c>
       <c r="I10" s="6">
         <f>'March 2026'!B11</f>
-        <v>46270</v>
-      </c>
-      <c r="J10" s="6" t="str">
+        <v>46272</v>
+      </c>
+      <c r="J10" s="6">
         <f>'March 2026'!O3</f>
-        <v/>
-      </c>
-      <c r="K10" s="18">
+        <v>46272</v>
+      </c>
+      <c r="K10" s="18" t="str">
         <f ca="1">'March 2026'!B12</f>
-        <v>4</v>
+        <v/>
       </c>
       <c r="L10" s="18" t="str">
         <f ca="1">'March 2026'!P3</f>
@@ -2591,11 +2685,11 @@
       </c>
       <c r="M10" s="3">
         <f>'March 2026'!K3</f>
-        <v>47.8</v>
+        <v>200.38</v>
       </c>
       <c r="N10" s="3">
         <f>'March 2026'!L3</f>
-        <v>0</v>
+        <v>9.11</v>
       </c>
       <c r="O10" s="3">
         <f>'March 2026'!M3</f>
@@ -2649,7 +2743,7 @@
       </c>
       <c r="K11" s="18">
         <f ca="1">'April 2026'!B12</f>
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="L11" s="18" t="str">
         <f ca="1">'April 2026'!P3</f>
@@ -2657,7 +2751,7 @@
       </c>
       <c r="M11" s="3">
         <f>'April 2026'!K3</f>
-        <v>43.2</v>
+        <v>54</v>
       </c>
       <c r="N11" s="3">
         <f>'April 2026'!L3</f>
@@ -2715,7 +2809,7 @@
       </c>
       <c r="K12" s="18">
         <f ca="1">'May 2026'!B12</f>
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="L12" s="18" t="str">
         <f ca="1">'May 2026'!P3</f>
@@ -2723,7 +2817,7 @@
       </c>
       <c r="M12" s="3">
         <f>'May 2026'!K3</f>
-        <v>18.39</v>
+        <v>24.52</v>
       </c>
       <c r="N12" s="3">
         <f>'May 2026'!L3</f>
@@ -2780,7 +2874,7 @@
       </c>
       <c r="K13" s="18">
         <f ca="1">'June 2026'!B12</f>
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="L13" s="18" t="str">
         <f ca="1">'June 2026'!P3</f>
@@ -2788,7 +2882,7 @@
       </c>
       <c r="M13" s="3">
         <f>'June 2026'!K3</f>
-        <v>8.2799999999999994</v>
+        <v>12.419999999999998</v>
       </c>
       <c r="N13" s="3">
         <f>'June 2026'!L3</f>
@@ -2845,7 +2939,7 @@
       </c>
       <c r="K14" s="18">
         <f ca="1">'July 2026'!B12</f>
-        <v>126</v>
+        <v>97</v>
       </c>
       <c r="L14" s="18" t="str">
         <f ca="1">'July 2026'!P3</f>
@@ -2853,7 +2947,7 @@
       </c>
       <c r="M14" s="3">
         <f>'July 2026'!K3</f>
-        <v>1.72</v>
+        <v>3.44</v>
       </c>
       <c r="N14" s="3">
         <f>'July 2026'!L3</f>
@@ -2910,7 +3004,7 @@
       </c>
       <c r="K15" s="18">
         <f ca="1">'August 2026'!B12</f>
-        <v>157</v>
+        <v>128</v>
       </c>
       <c r="L15" s="18" t="str">
         <f ca="1">'August 2026'!P3</f>
@@ -2918,7 +3012,7 @@
       </c>
       <c r="M15" s="3">
         <f>'August 2026'!K3</f>
-        <v>0</v>
+        <v>13.02</v>
       </c>
       <c r="N15" s="3">
         <f>'August 2026'!L3</f>
@@ -2934,22 +3028,69 @@
       </c>
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A16" s="2"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="18"/>
-      <c r="L16" s="18"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="3"/>
-      <c r="AC16" s="1"/>
+      <c r="A16" s="2">
+        <v>14</v>
+      </c>
+      <c r="B16" s="6">
+        <f>'September 2026'!B9</f>
+        <v>46279</v>
+      </c>
+      <c r="C16" s="24" t="str">
+        <f>'September 2026'!B1</f>
+        <v>September 2026</v>
+      </c>
+      <c r="D16" s="2" t="str">
+        <f>'September 2026'!B2</f>
+        <v>Estonia</v>
+      </c>
+      <c r="E16" s="2" t="str">
+        <f>'September 2026'!B3</f>
+        <v>Scramble</v>
+      </c>
+      <c r="F16" s="2" t="str">
+        <f>'September 2026'!B8</f>
+        <v>0 m. 5 mėn. 19 d.</v>
+      </c>
+      <c r="G16" s="7" t="str">
+        <f>'September 2026'!B15</f>
+        <v>9-12%</v>
+      </c>
+      <c r="H16" s="3">
+        <f>'September 2026'!B16</f>
+        <v>197.5</v>
+      </c>
+      <c r="I16" s="6">
+        <f>'September 2026'!B11</f>
+        <v>46451</v>
+      </c>
+      <c r="J16" s="6" t="str">
+        <f>'September 2026'!O3</f>
+        <v/>
+      </c>
+      <c r="K16" s="18">
+        <f ca="1">'September 2026'!B12</f>
+        <v>156</v>
+      </c>
+      <c r="L16" s="18" t="str">
+        <f ca="1">'September 2026'!P3</f>
+        <v/>
+      </c>
+      <c r="M16" s="3">
+        <f>'September 2026'!K3</f>
+        <v>0</v>
+      </c>
+      <c r="N16" s="3">
+        <f>'September 2026'!L3</f>
+        <v>0</v>
+      </c>
+      <c r="O16" s="3">
+        <f>'September 2026'!M3</f>
+        <v>0</v>
+      </c>
+      <c r="AC16" s="3" t="str">
+        <f ca="1">'September 2026'!Z3</f>
+        <v/>
+      </c>
     </row>
     <row r="17" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
@@ -3123,20 +3264,20 @@
     <mergeCell ref="U1:V1"/>
   </mergeCells>
   <conditionalFormatting sqref="A3:O25">
-    <cfRule type="expression" dxfId="55" priority="9">
+    <cfRule type="expression" dxfId="59" priority="9">
       <formula>$AC3="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="54" priority="13">
+    <cfRule type="expression" dxfId="58" priority="13">
       <formula>AND($H3&gt;0,$H3=$M3)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC3:AC25">
-    <cfRule type="expression" dxfId="53" priority="2">
+    <cfRule type="expression" dxfId="57" priority="2">
       <formula>AND($H3&gt;0,$H3=$M3)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC6:AC15">
-    <cfRule type="expression" dxfId="52" priority="1">
+  <conditionalFormatting sqref="AC6:AC16">
+    <cfRule type="expression" dxfId="56" priority="1">
       <formula>$AC6="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3154,6 +3295,7 @@
     <hyperlink ref="C13" location="'June 2026'!A1" display="'June 2026'!A1" xr:uid="{D41A3630-A56F-4916-B1AA-C5C3695F19A8}"/>
     <hyperlink ref="C14" location="'July 2026'!A1" display="'July 2026'!A1" xr:uid="{8B58AC79-8F19-4849-BA55-1D38985B2EEB}"/>
     <hyperlink ref="C15" location="'August 2026'!A1" display="'August 2026'!A1" xr:uid="{6EA87317-B9C8-43E4-8AE8-6D1BF358572F}"/>
+    <hyperlink ref="C16" location="'September 2026'!A1" display="'September 2026'!A1" xr:uid="{76FDE0B3-A187-4C19-82A3-3B813BD03F8C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3161,6 +3303,1340 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B8F9EBE-D214-44A2-8A19-768E491F391C}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
+  <dimension ref="A1:Z53"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="40.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="9" width="10.7109375" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" customWidth="1"/>
+    <col min="11" max="14" width="10.7109375" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" customWidth="1"/>
+    <col min="16" max="17" width="10.7109375" customWidth="1"/>
+    <col min="18" max="23" width="8.7109375" customWidth="1"/>
+    <col min="24" max="24" width="12.7109375" style="13" customWidth="1"/>
+    <col min="25" max="25" width="10.7109375" style="13" customWidth="1"/>
+    <col min="26" max="26" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="36" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="37"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="37"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
+      <c r="Q1" s="38"/>
+      <c r="X1" s="36"/>
+      <c r="Y1" s="37"/>
+      <c r="Z1" s="38"/>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="9"/>
+      <c r="K2" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O2" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="P2" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q2" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="X2" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y2" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z2" s="11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" s="6">
+        <v>46086</v>
+      </c>
+      <c r="E3" s="6">
+        <v>46086</v>
+      </c>
+      <c r="F3" s="18">
+        <f t="shared" ref="F3:F52" si="0">IF(E3&gt;0,E3-D3,"")</f>
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>10.86</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0</v>
+      </c>
+      <c r="J3" s="13"/>
+      <c r="K3" s="3">
+        <f>G53</f>
+        <v>198.85</v>
+      </c>
+      <c r="L3" s="3">
+        <f>H53</f>
+        <v>8.85</v>
+      </c>
+      <c r="M3" s="3">
+        <f>I53</f>
+        <v>0</v>
+      </c>
+      <c r="N3" s="7">
+        <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
+        <v>0.10662775635719302</v>
+      </c>
+      <c r="O3" s="6">
+        <f>IF(B16=K3,MAX(E:E),"")</f>
+        <v>46239</v>
+      </c>
+      <c r="P3" s="2" t="str">
+        <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
+        <v/>
+      </c>
+      <c r="Q3" s="2">
+        <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
+        <v>0</v>
+      </c>
+      <c r="T3" s="15"/>
+      <c r="X3" s="6">
+        <f>B9</f>
+        <v>46058</v>
+      </c>
+      <c r="Y3" s="3">
+        <f>B16*-1</f>
+        <v>-198.85</v>
+      </c>
+      <c r="Z3" s="2" t="str">
+        <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="6">
+        <v>46118</v>
+      </c>
+      <c r="E4" s="6">
+        <v>46118</v>
+      </c>
+      <c r="F4" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="2">
+        <v>10.76</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3">
+        <v>0</v>
+      </c>
+      <c r="J4" s="9"/>
+      <c r="X4" s="6">
+        <f>E3</f>
+        <v>46086</v>
+      </c>
+      <c r="Y4" s="3">
+        <f>G3+H3-I3</f>
+        <v>10.86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A5" s="5"/>
+      <c r="B5" s="6"/>
+      <c r="D5" s="6">
+        <v>46147</v>
+      </c>
+      <c r="E5" s="6">
+        <v>46147</v>
+      </c>
+      <c r="F5" s="18">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2">
+        <v>10.96</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3">
+        <v>0</v>
+      </c>
+      <c r="J5" s="9"/>
+      <c r="X5" s="6">
+        <f t="shared" ref="X5:X52" si="1">E4</f>
+        <v>46118</v>
+      </c>
+      <c r="Y5" s="3">
+        <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
+        <v>10.76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A6" s="5"/>
+      <c r="B6" s="6"/>
+      <c r="D6" s="6">
+        <v>46178</v>
+      </c>
+      <c r="E6" s="6">
+        <v>46178</v>
+      </c>
+      <c r="F6" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="2">
+        <v>10.76</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3">
+        <v>0</v>
+      </c>
+      <c r="J6" s="9"/>
+      <c r="X6" s="6">
+        <f t="shared" si="1"/>
+        <v>46147</v>
+      </c>
+      <c r="Y6" s="3">
+        <f t="shared" si="2"/>
+        <v>10.96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A7" s="5"/>
+      <c r="B7" s="6"/>
+      <c r="D7" s="6">
+        <v>46209</v>
+      </c>
+      <c r="E7" s="6">
+        <v>46209</v>
+      </c>
+      <c r="F7" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G7" s="2">
+        <v>10.76</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3">
+        <v>0</v>
+      </c>
+      <c r="J7" s="13"/>
+      <c r="X7" s="6">
+        <f t="shared" si="1"/>
+        <v>46178</v>
+      </c>
+      <c r="Y7" s="3">
+        <f t="shared" si="2"/>
+        <v>10.76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="6" t="str">
+        <f>DATEDIF(B9,B11,"y") &amp; " m. " &amp; DATEDIF(B9,B11,"ym") &amp; " mėn. " &amp; DATEDIF(B9,B11,"md") &amp; " d."</f>
+        <v>0 m. 6 mėn. 0 d.</v>
+      </c>
+      <c r="D8" s="6">
+        <v>46239</v>
+      </c>
+      <c r="E8" s="6">
+        <v>46239</v>
+      </c>
+      <c r="F8" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G8" s="2">
+        <v>144.75</v>
+      </c>
+      <c r="H8" s="3">
+        <v>8.85</v>
+      </c>
+      <c r="I8" s="3">
+        <v>0</v>
+      </c>
+      <c r="J8" s="9"/>
+      <c r="X8" s="6">
+        <f t="shared" si="1"/>
+        <v>46209</v>
+      </c>
+      <c r="Y8" s="3">
+        <f t="shared" si="2"/>
+        <v>10.76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="6">
+        <v>46058</v>
+      </c>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G9" s="2"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="13"/>
+      <c r="X9" s="6">
+        <f t="shared" si="1"/>
+        <v>46239</v>
+      </c>
+      <c r="Y9" s="3">
+        <f t="shared" si="2"/>
+        <v>153.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="6">
+        <v>46070</v>
+      </c>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="13"/>
+      <c r="X10" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y10" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <v>46239</v>
+      </c>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G11" s="3"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="13"/>
+      <c r="X11" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y11" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="18" t="str">
+        <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G12" s="3"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="13"/>
+      <c r="X12" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y12" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A13" s="5"/>
+      <c r="B13" s="3"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="13"/>
+      <c r="N13" s="15"/>
+      <c r="X13" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="19"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="13"/>
+      <c r="X14" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="10"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="17"/>
+      <c r="M15" s="17"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="17"/>
+      <c r="X15" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="3">
+        <v>198.85</v>
+      </c>
+      <c r="D16" s="10"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="21"/>
+      <c r="P16" s="13"/>
+      <c r="Q16" s="13"/>
+      <c r="X16" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y16" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D17" s="10"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="13"/>
+      <c r="X17" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y17" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D18" s="10"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="13"/>
+      <c r="X18" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y18" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D19" s="10"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="13"/>
+      <c r="X19" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y19" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D20" s="10"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="13"/>
+      <c r="X20" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D21" s="10"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="13"/>
+      <c r="X21" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y21" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D22" s="10"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="13"/>
+      <c r="X22" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D23" s="10"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="13"/>
+      <c r="X23" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y23" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D24" s="10"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="13"/>
+      <c r="X24" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D25" s="10"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="13"/>
+      <c r="X25" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D26" s="10"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="13"/>
+      <c r="X26" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y26" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D27" s="10"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="13"/>
+      <c r="X27" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y27" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D28" s="10"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="13"/>
+      <c r="X28" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D29" s="10"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="13"/>
+      <c r="X29" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D30" s="10"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="13"/>
+      <c r="X30" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D31" s="10"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="13"/>
+      <c r="X31" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D32" s="10"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="13"/>
+      <c r="X32" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D33" s="10"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="13"/>
+      <c r="X33" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y33" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D34" s="10"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="13"/>
+      <c r="X34" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D35" s="10"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="13"/>
+      <c r="X35" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y35" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D36" s="10"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="13"/>
+      <c r="X36" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y36" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D37" s="10"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="13"/>
+      <c r="X37" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y37" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D38" s="10"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="13"/>
+      <c r="X38" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y38" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D39" s="10"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="13"/>
+      <c r="X39" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y39" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D40" s="10"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="13"/>
+      <c r="X40" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y40" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D41" s="10"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="13"/>
+      <c r="X41" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y41" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D42" s="10"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="13"/>
+      <c r="X42" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D43" s="10"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="13"/>
+      <c r="X43" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y43" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D44" s="10"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="13"/>
+      <c r="X44" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y44" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D45" s="10"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="13"/>
+      <c r="X45" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y45" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D46" s="10"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="13"/>
+      <c r="X46" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y46" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D47" s="10"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="13"/>
+      <c r="X47" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D48" s="10"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="13"/>
+      <c r="X48" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y48" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D49" s="10"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="13"/>
+      <c r="X49" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y49" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D50" s="10"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="13"/>
+      <c r="X50" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D51" s="10"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="13"/>
+      <c r="X51" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D52" s="10"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="9"/>
+      <c r="X52" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y52" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D53" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E53" s="14"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3">
+        <f>SUM(G3:G52)</f>
+        <v>198.85</v>
+      </c>
+      <c r="H53" s="3">
+        <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
+        <v>8.85</v>
+      </c>
+      <c r="I53" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="X1:Z1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="expression" dxfId="27" priority="1">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="26" priority="2">
+      <formula>$B$16=$K$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P3">
+    <cfRule type="expression" dxfId="25" priority="9">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z3">
+    <cfRule type="expression" dxfId="24" priority="10">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E465F013-9FF2-44FD-828F-D999C3230D4E}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -3190,29 +4666,29 @@
       <c r="B1" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="34" t="s">
+      <c r="D1" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="35"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="35"/>
-      <c r="I1" s="36"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="37"/>
+      <c r="I1" s="38"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="34" t="s">
+      <c r="K1" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="36"/>
-      <c r="X1" s="34"/>
-      <c r="Y1" s="35"/>
-      <c r="Z1" s="36"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
+      <c r="Q1" s="38"/>
+      <c r="X1" s="36"/>
+      <c r="Y1" s="37"/>
+      <c r="Z1" s="38"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -3304,7 +4780,7 @@
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
@@ -3312,7 +4788,7 @@
       </c>
       <c r="N3" s="7">
         <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
-        <v>0.10611786246299745</v>
+        <v>0.10550422072410584</v>
       </c>
       <c r="O3" s="6">
         <f>IF(B16=K3,MAX(E:E),"")</f>
@@ -3494,7 +4970,7 @@
         <v>28.65</v>
       </c>
       <c r="H8" s="3">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="I8" s="3">
         <v>0</v>
@@ -3529,7 +5005,7 @@
       </c>
       <c r="Y9" s="3">
         <f t="shared" si="2"/>
-        <v>30.419999999999998</v>
+        <v>30.41</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
@@ -4454,7 +5930,7 @@
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
@@ -4492,7 +5968,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1D1CAB2-9974-4180-AFF6-5274525FE544}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -4522,29 +5998,29 @@
       <c r="B1" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="D1" s="34" t="s">
+      <c r="D1" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="35"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="35"/>
-      <c r="I1" s="36"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="37"/>
+      <c r="I1" s="38"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="34" t="s">
+      <c r="K1" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="36"/>
-      <c r="X1" s="34"/>
-      <c r="Y1" s="35"/>
-      <c r="Z1" s="36"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
+      <c r="Q1" s="38"/>
+      <c r="X1" s="36"/>
+      <c r="Y1" s="37"/>
+      <c r="Z1" s="38"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -5818,7 +7294,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3754DA4B-78B4-44BD-BB4B-39C6D453FDD0}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -5848,29 +7324,29 @@
       <c r="B1" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="34" t="s">
+      <c r="D1" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="35"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="35"/>
-      <c r="I1" s="36"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="37"/>
+      <c r="I1" s="38"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="34" t="s">
+      <c r="K1" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="36"/>
-      <c r="X1" s="34"/>
-      <c r="Y1" s="35"/>
-      <c r="Z1" s="36"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
+      <c r="Q1" s="38"/>
+      <c r="X1" s="36"/>
+      <c r="Y1" s="37"/>
+      <c r="Z1" s="38"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -7144,7 +8620,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A46497B-E391-4B8F-8947-28547C504629}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -7174,29 +8650,29 @@
       <c r="B1" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D1" s="34" t="s">
+      <c r="D1" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="35"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="35"/>
-      <c r="I1" s="36"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="37"/>
+      <c r="I1" s="38"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="34" t="s">
+      <c r="K1" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="36"/>
-      <c r="X1" s="34"/>
-      <c r="Y1" s="35"/>
-      <c r="Z1" s="36"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
+      <c r="Q1" s="38"/>
+      <c r="X1" s="36"/>
+      <c r="Y1" s="37"/>
+      <c r="Z1" s="38"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -8464,7 +9940,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BE44972-B3BE-4780-9CE5-89011043CB83}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -8494,29 +9970,29 @@
       <c r="B1" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="34" t="s">
+      <c r="D1" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="35"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="35"/>
-      <c r="I1" s="36"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="37"/>
+      <c r="I1" s="38"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="34" t="s">
+      <c r="K1" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="36"/>
-      <c r="X1" s="34"/>
-      <c r="Y1" s="35"/>
-      <c r="Z1" s="36"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
+      <c r="Q1" s="38"/>
+      <c r="X1" s="36"/>
+      <c r="Y1" s="37"/>
+      <c r="Z1" s="38"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -9784,7 +11260,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -9814,29 +11290,29 @@
       <c r="B1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="34" t="s">
+      <c r="D1" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="35"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="35"/>
-      <c r="I1" s="36"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="37"/>
+      <c r="I1" s="38"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="34" t="s">
+      <c r="K1" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="36"/>
-      <c r="X1" s="34"/>
-      <c r="Y1" s="35"/>
-      <c r="Z1" s="36"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
+      <c r="Q1" s="38"/>
+      <c r="X1" s="36"/>
+      <c r="Y1" s="37"/>
+      <c r="Z1" s="38"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -12637,14 +14113,14 @@
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="6">
         <f ca="1">TODAY()</f>
-        <v>46266</v>
+        <v>46295</v>
       </c>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
       <c r="D200" s="1"/>
       <c r="K200" s="25">
         <f>Overview!W3</f>
-        <v>678.49</v>
+        <v>687.59</v>
       </c>
     </row>
   </sheetData>
@@ -12653,6 +14129,1290 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB14D149-944D-412E-95CC-4C7E13B9E24E}">
+  <dimension ref="A1:Z53"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="40.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="9" width="10.7109375" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" customWidth="1"/>
+    <col min="11" max="14" width="10.7109375" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" customWidth="1"/>
+    <col min="16" max="17" width="10.7109375" customWidth="1"/>
+    <col min="18" max="23" width="8.7109375" customWidth="1"/>
+    <col min="24" max="24" width="12.7109375" style="13" customWidth="1"/>
+    <col min="25" max="25" width="10.7109375" style="13" customWidth="1"/>
+    <col min="26" max="26" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="36" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="37"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="37"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
+      <c r="Q1" s="38"/>
+      <c r="X1" s="36"/>
+      <c r="Y1" s="37"/>
+      <c r="Z1" s="38"/>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="34" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="9"/>
+      <c r="K2" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" s="35" t="s">
+        <v>22</v>
+      </c>
+      <c r="O2" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="P2" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q2" s="35" t="s">
+        <v>29</v>
+      </c>
+      <c r="X2" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y2" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z2" s="35" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" s="6">
+        <v>46300</v>
+      </c>
+      <c r="E3" s="6"/>
+      <c r="F3" s="18" t="str">
+        <f t="shared" ref="F3:F52" si="0">IF(E3&gt;0,E3-D3,"")</f>
+        <v/>
+      </c>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="3">
+        <f>G53</f>
+        <v>0</v>
+      </c>
+      <c r="L3" s="3">
+        <f>H53</f>
+        <v>0</v>
+      </c>
+      <c r="M3" s="3">
+        <f>I53</f>
+        <v>0</v>
+      </c>
+      <c r="N3" s="7" t="str">
+        <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
+        <v/>
+      </c>
+      <c r="O3" s="6" t="str">
+        <f>IF(B16=K3,MAX(E:E),"")</f>
+        <v/>
+      </c>
+      <c r="P3" s="2" t="str">
+        <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
+        <v/>
+      </c>
+      <c r="Q3" s="2" t="str">
+        <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
+        <v/>
+      </c>
+      <c r="T3" s="15"/>
+      <c r="X3" s="6">
+        <f>B9</f>
+        <v>46279</v>
+      </c>
+      <c r="Y3" s="3">
+        <f>B16*-1</f>
+        <v>-197.5</v>
+      </c>
+      <c r="Z3" s="2" t="str">
+        <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="6">
+        <v>46331</v>
+      </c>
+      <c r="E4" s="6"/>
+      <c r="F4" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="9"/>
+      <c r="X4" s="6">
+        <f>E3</f>
+        <v>0</v>
+      </c>
+      <c r="Y4" s="3">
+        <f>G3+H3-I3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A5" s="5"/>
+      <c r="B5" s="6"/>
+      <c r="D5" s="6">
+        <v>46361</v>
+      </c>
+      <c r="E5" s="6"/>
+      <c r="F5" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="9"/>
+      <c r="X5" s="6">
+        <f t="shared" ref="X5:X52" si="1">E4</f>
+        <v>0</v>
+      </c>
+      <c r="Y5" s="3">
+        <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A6" s="5"/>
+      <c r="B6" s="6"/>
+      <c r="D6" s="6">
+        <v>46392</v>
+      </c>
+      <c r="E6" s="6"/>
+      <c r="F6" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="9"/>
+      <c r="X6" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A7" s="5"/>
+      <c r="B7" s="6"/>
+      <c r="D7" s="6">
+        <v>46423</v>
+      </c>
+      <c r="E7" s="6"/>
+      <c r="F7" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="13"/>
+      <c r="X7" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="6" t="str">
+        <f>DATEDIF(B9,B11,"y") &amp; " m. " &amp; DATEDIF(B9,B11,"ym") &amp; " mėn. " &amp; DATEDIF(B9,B11,"md") &amp; " d."</f>
+        <v>0 m. 5 mėn. 19 d.</v>
+      </c>
+      <c r="D8" s="6">
+        <v>46451</v>
+      </c>
+      <c r="E8" s="6"/>
+      <c r="F8" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G8" s="2"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="9"/>
+      <c r="X8" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="6">
+        <v>46279</v>
+      </c>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G9" s="2"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="13"/>
+      <c r="X9" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="6">
+        <v>46282</v>
+      </c>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="13"/>
+      <c r="X10" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y10" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <v>46451</v>
+      </c>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G11" s="3"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="13"/>
+      <c r="X11" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y11" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="18">
+        <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
+        <v>156</v>
+      </c>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G12" s="3"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="13"/>
+      <c r="X12" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y12" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A13" s="5"/>
+      <c r="B13" s="3"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="13"/>
+      <c r="N13" s="15"/>
+      <c r="X13" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="19"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="13"/>
+      <c r="X14" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="10"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="17"/>
+      <c r="M15" s="17"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="17"/>
+      <c r="X15" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="3">
+        <v>197.5</v>
+      </c>
+      <c r="D16" s="10"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="21"/>
+      <c r="P16" s="13"/>
+      <c r="Q16" s="13"/>
+      <c r="X16" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y16" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D17" s="10"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="13"/>
+      <c r="X17" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y17" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D18" s="10"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="13"/>
+      <c r="X18" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y18" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D19" s="10"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="13"/>
+      <c r="X19" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y19" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D20" s="10"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="13"/>
+      <c r="X20" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D21" s="10"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="13"/>
+      <c r="X21" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y21" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D22" s="10"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="13"/>
+      <c r="X22" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D23" s="10"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="13"/>
+      <c r="X23" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y23" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D24" s="10"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="13"/>
+      <c r="X24" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D25" s="10"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="13"/>
+      <c r="X25" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D26" s="10"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="13"/>
+      <c r="X26" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y26" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D27" s="10"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="13"/>
+      <c r="X27" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y27" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D28" s="10"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="13"/>
+      <c r="X28" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D29" s="10"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="13"/>
+      <c r="X29" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D30" s="10"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="13"/>
+      <c r="X30" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D31" s="10"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="13"/>
+      <c r="X31" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D32" s="10"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="13"/>
+      <c r="X32" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D33" s="10"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="13"/>
+      <c r="X33" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y33" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D34" s="10"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="13"/>
+      <c r="X34" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D35" s="10"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="13"/>
+      <c r="X35" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y35" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D36" s="10"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="13"/>
+      <c r="X36" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y36" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D37" s="10"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="13"/>
+      <c r="X37" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y37" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D38" s="10"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="13"/>
+      <c r="X38" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y38" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D39" s="10"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="13"/>
+      <c r="X39" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y39" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D40" s="10"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="13"/>
+      <c r="X40" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y40" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D41" s="10"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="13"/>
+      <c r="X41" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y41" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D42" s="10"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="13"/>
+      <c r="X42" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D43" s="10"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="13"/>
+      <c r="X43" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y43" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D44" s="10"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="13"/>
+      <c r="X44" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y44" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D45" s="10"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="13"/>
+      <c r="X45" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y45" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D46" s="10"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="13"/>
+      <c r="X46" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y46" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D47" s="10"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="13"/>
+      <c r="X47" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D48" s="10"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="13"/>
+      <c r="X48" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y48" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D49" s="10"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="13"/>
+      <c r="X49" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y49" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D50" s="10"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="13"/>
+      <c r="X50" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D51" s="10"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="13"/>
+      <c r="X51" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D52" s="10"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="9"/>
+      <c r="X52" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y52" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D53" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E53" s="14"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3">
+        <f>SUM(G3:G52)</f>
+        <v>0</v>
+      </c>
+      <c r="H53" s="3">
+        <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
+        <v>0</v>
+      </c>
+      <c r="I53" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="X1:Z1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="expression" dxfId="55" priority="1">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="54" priority="2">
+      <formula>$B$16=$K$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P3">
+    <cfRule type="expression" dxfId="53" priority="3">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z3">
+    <cfRule type="expression" dxfId="52" priority="4">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40E5D5DD-CBD2-4FD8-9F41-16B9523FDC2D}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -12679,29 +15439,29 @@
       <c r="B1" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="D1" s="34" t="s">
+      <c r="D1" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="35"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="35"/>
-      <c r="I1" s="36"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="37"/>
+      <c r="I1" s="38"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="34" t="s">
+      <c r="K1" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="36"/>
-      <c r="X1" s="34"/>
-      <c r="Y1" s="35"/>
-      <c r="Z1" s="36"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
+      <c r="Q1" s="38"/>
+      <c r="X1" s="36"/>
+      <c r="Y1" s="37"/>
+      <c r="Z1" s="38"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -12768,20 +15528,28 @@
         <v>42</v>
       </c>
       <c r="D3" s="6">
-        <v>46270</v>
-      </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="18" t="str">
+        <v>46272</v>
+      </c>
+      <c r="E3" s="6">
+        <v>46272</v>
+      </c>
+      <c r="F3" s="18">
         <f t="shared" ref="F3:F52" si="0">IF(E3&gt;0,E3-D3,"")</f>
-        <v/>
-      </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>13.02</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0</v>
+      </c>
       <c r="J3" s="13"/>
       <c r="K3" s="3">
         <f>G53</f>
-        <v>0</v>
+        <v>13.02</v>
       </c>
       <c r="L3" s="3">
         <f>H53</f>
@@ -12842,11 +15610,11 @@
       <c r="J4" s="9"/>
       <c r="X4" s="6">
         <f>E3</f>
-        <v>0</v>
+        <v>46272</v>
       </c>
       <c r="Y4" s="3">
         <f>G3+H3-I3</f>
-        <v>0</v>
+        <v>13.02</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
@@ -13034,7 +15802,7 @@
       </c>
       <c r="B12" s="18">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>157</v>
+        <v>128</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -13894,7 +16662,7 @@
       <c r="F53" s="3"/>
       <c r="G53" s="3">
         <f>SUM(G3:G52)</f>
-        <v>0</v>
+        <v>13.02</v>
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
@@ -13936,7 +16704,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EA74071-CEE0-4172-8957-6D5916CFD11C}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -13963,29 +16731,29 @@
       <c r="B1" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="34" t="s">
+      <c r="D1" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="35"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="35"/>
-      <c r="I1" s="36"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="37"/>
+      <c r="I1" s="38"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="34" t="s">
+      <c r="K1" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="36"/>
-      <c r="X1" s="34"/>
-      <c r="Y1" s="35"/>
-      <c r="Z1" s="36"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
+      <c r="Q1" s="38"/>
+      <c r="X1" s="36"/>
+      <c r="Y1" s="37"/>
+      <c r="Z1" s="38"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -14073,7 +16841,7 @@
       <c r="J3" s="13"/>
       <c r="K3" s="3">
         <f>G53</f>
-        <v>1.72</v>
+        <v>3.44</v>
       </c>
       <c r="L3" s="3">
         <f>H53</f>
@@ -14121,16 +16889,24 @@
         <v>44</v>
       </c>
       <c r="D4" s="6">
-        <v>46270</v>
-      </c>
-      <c r="E4" s="6"/>
-      <c r="F4" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+        <v>46272</v>
+      </c>
+      <c r="E4" s="6">
+        <v>46272</v>
+      </c>
+      <c r="F4" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>1.72</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3">
+        <v>0</v>
+      </c>
       <c r="J4" s="9"/>
       <c r="X4" s="6">
         <f>E3</f>
@@ -14158,11 +16934,11 @@
       <c r="J5" s="9"/>
       <c r="X5" s="6">
         <f t="shared" ref="X5:X52" si="1">E4</f>
-        <v>0</v>
+        <v>46272</v>
       </c>
       <c r="Y5" s="3">
         <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
-        <v>0</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
@@ -14326,7 +17102,7 @@
       </c>
       <c r="B12" s="18">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>126</v>
+        <v>97</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -15186,7 +17962,7 @@
       <c r="F53" s="3"/>
       <c r="G53" s="3">
         <f>SUM(G3:G52)</f>
-        <v>1.72</v>
+        <v>3.44</v>
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
@@ -15228,7 +18004,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E39A4C94-8C03-41D4-B944-5DB24FED2BD0}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -15255,29 +18031,29 @@
       <c r="B1" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D1" s="34" t="s">
+      <c r="D1" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="35"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="35"/>
-      <c r="I1" s="36"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="37"/>
+      <c r="I1" s="38"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="34" t="s">
+      <c r="K1" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="36"/>
-      <c r="X1" s="34"/>
-      <c r="Y1" s="35"/>
-      <c r="Z1" s="36"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
+      <c r="Q1" s="38"/>
+      <c r="X1" s="36"/>
+      <c r="Y1" s="37"/>
+      <c r="Z1" s="38"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -15365,7 +18141,7 @@
       <c r="J3" s="13"/>
       <c r="K3" s="3">
         <f>G53</f>
-        <v>8.2799999999999994</v>
+        <v>12.419999999999998</v>
       </c>
       <c r="L3" s="3">
         <f>H53</f>
@@ -15444,16 +18220,24 @@
       <c r="A5" s="5"/>
       <c r="B5" s="6"/>
       <c r="D5" s="6">
-        <v>46270</v>
-      </c>
-      <c r="E5" s="6"/>
-      <c r="F5" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
+        <v>46272</v>
+      </c>
+      <c r="E5" s="6">
+        <v>46272</v>
+      </c>
+      <c r="F5" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <v>4.1399999999999997</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3">
+        <v>0</v>
+      </c>
       <c r="J5" s="9"/>
       <c r="X5" s="6">
         <f t="shared" ref="X5:X52" si="1">E4</f>
@@ -15481,11 +18265,11 @@
       <c r="J6" s="9"/>
       <c r="X6" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46272</v>
       </c>
       <c r="Y6" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4.1399999999999997</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
@@ -15625,7 +18409,7 @@
       </c>
       <c r="B12" s="18">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -16485,7 +19269,7 @@
       <c r="F53" s="3"/>
       <c r="G53" s="3">
         <f>SUM(G3:G52)</f>
-        <v>8.2799999999999994</v>
+        <v>12.419999999999998</v>
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
@@ -16527,7 +19311,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51596B63-3E30-4F0D-ACA7-3B11B25E71A9}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -16554,29 +19338,29 @@
       <c r="B1" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="34" t="s">
+      <c r="D1" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="35"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="35"/>
-      <c r="I1" s="36"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="37"/>
+      <c r="I1" s="38"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="34" t="s">
+      <c r="K1" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="36"/>
-      <c r="X1" s="34"/>
-      <c r="Y1" s="35"/>
-      <c r="Z1" s="36"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
+      <c r="Q1" s="38"/>
+      <c r="X1" s="36"/>
+      <c r="Y1" s="37"/>
+      <c r="Z1" s="38"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -16664,7 +19448,7 @@
       <c r="J3" s="13"/>
       <c r="K3" s="3">
         <f>G53</f>
-        <v>18.39</v>
+        <v>24.52</v>
       </c>
       <c r="L3" s="3">
         <f>H53</f>
@@ -16776,16 +19560,24 @@
       <c r="A6" s="5"/>
       <c r="B6" s="6"/>
       <c r="D6" s="6">
-        <v>46270</v>
-      </c>
-      <c r="E6" s="6"/>
-      <c r="F6" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
+        <v>46272</v>
+      </c>
+      <c r="E6" s="6">
+        <v>46272</v>
+      </c>
+      <c r="F6" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="2">
+        <v>6.13</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3">
+        <v>0</v>
+      </c>
       <c r="J6" s="9"/>
       <c r="X6" s="6">
         <f t="shared" si="1"/>
@@ -16813,11 +19605,11 @@
       <c r="J7" s="13"/>
       <c r="X7" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46272</v>
       </c>
       <c r="Y7" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6.13</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
@@ -16933,7 +19725,7 @@
       </c>
       <c r="B12" s="18">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -17793,7 +20585,7 @@
       <c r="F53" s="3"/>
       <c r="G53" s="3">
         <f>SUM(G3:G52)</f>
-        <v>18.39</v>
+        <v>24.52</v>
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
@@ -17835,7 +20627,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6787A89-4537-4E64-91BF-0AA0F96019C3}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -17862,29 +20654,29 @@
       <c r="B1" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="D1" s="34" t="s">
+      <c r="D1" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="35"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="35"/>
-      <c r="I1" s="36"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="37"/>
+      <c r="I1" s="38"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="34" t="s">
+      <c r="K1" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="36"/>
-      <c r="X1" s="34"/>
-      <c r="Y1" s="35"/>
-      <c r="Z1" s="36"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
+      <c r="Q1" s="38"/>
+      <c r="X1" s="36"/>
+      <c r="Y1" s="37"/>
+      <c r="Z1" s="38"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -17972,7 +20764,7 @@
       <c r="J3" s="13"/>
       <c r="K3" s="3">
         <f>G53</f>
-        <v>43.2</v>
+        <v>54</v>
       </c>
       <c r="L3" s="3">
         <f>H53</f>
@@ -18116,16 +20908,24 @@
       <c r="A7" s="5"/>
       <c r="B7" s="6"/>
       <c r="D7" s="6">
-        <v>46270</v>
-      </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
+        <v>46272</v>
+      </c>
+      <c r="E7" s="6">
+        <v>46272</v>
+      </c>
+      <c r="F7" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>10.8</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3">
+        <v>0</v>
+      </c>
       <c r="J7" s="13"/>
       <c r="X7" s="6">
         <f t="shared" si="1"/>
@@ -18158,11 +20958,11 @@
       <c r="J8" s="9"/>
       <c r="X8" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46272</v>
       </c>
       <c r="Y8" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
@@ -18249,7 +21049,7 @@
       </c>
       <c r="B12" s="18">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -19109,7 +21909,7 @@
       <c r="F53" s="3"/>
       <c r="G53" s="3">
         <f>SUM(G3:G52)</f>
-        <v>43.2</v>
+        <v>54</v>
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
@@ -19151,8 +21951,11 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29B83440-5743-4944-A92C-7C00476AA6BD}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -19178,29 +21981,29 @@
       <c r="B1" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="D1" s="34" t="s">
+      <c r="D1" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="35"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="35"/>
-      <c r="I1" s="36"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="37"/>
+      <c r="I1" s="38"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="34" t="s">
+      <c r="K1" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="36"/>
-      <c r="X1" s="34"/>
-      <c r="Y1" s="35"/>
-      <c r="Z1" s="36"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
+      <c r="Q1" s="38"/>
+      <c r="X1" s="36"/>
+      <c r="Y1" s="37"/>
+      <c r="Z1" s="38"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -19288,31 +22091,31 @@
       <c r="J3" s="13"/>
       <c r="K3" s="3">
         <f>G53</f>
-        <v>47.8</v>
+        <v>200.38</v>
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>0</v>
+        <v>9.11</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
         <v>0</v>
       </c>
-      <c r="N3" s="7" t="str">
+      <c r="N3" s="7">
         <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
-        <v/>
-      </c>
-      <c r="O3" s="6" t="str">
+        <v>0.10385321974754333</v>
+      </c>
+      <c r="O3" s="6">
         <f>IF(B16=K3,MAX(E:E),"")</f>
-        <v/>
+        <v>46272</v>
       </c>
       <c r="P3" s="2" t="str">
         <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
         <v/>
       </c>
-      <c r="Q3" s="2" t="str">
+      <c r="Q3" s="2">
         <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T3" s="15"/>
       <c r="X3" s="6">
@@ -19466,19 +22269,27 @@
       </c>
       <c r="B8" s="6" t="str">
         <f>DATEDIF(B9,B11,"y") &amp; " m. " &amp; DATEDIF(B9,B11,"ym") &amp; " mėn. " &amp; DATEDIF(B9,B11,"md") &amp; " d."</f>
-        <v>0 m. 6 mėn. 0 d.</v>
+        <v>0 m. 6 mėn. 2 d.</v>
       </c>
       <c r="D8" s="6">
         <v>46272</v>
       </c>
-      <c r="E8" s="6"/>
-      <c r="F8" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
+      <c r="E8" s="6">
+        <v>46272</v>
+      </c>
+      <c r="F8" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G8" s="2">
+        <v>152.58000000000001</v>
+      </c>
+      <c r="H8" s="3">
+        <v>9.11</v>
+      </c>
+      <c r="I8" s="3">
+        <v>0</v>
+      </c>
       <c r="J8" s="9"/>
       <c r="X8" s="6">
         <f t="shared" si="1"/>
@@ -19508,11 +22319,11 @@
       <c r="J9" s="13"/>
       <c r="X9" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46272</v>
       </c>
       <c r="Y9" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>161.69</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
@@ -19546,7 +22357,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="6">
-        <v>46270</v>
+        <v>46272</v>
       </c>
       <c r="D11" s="10"/>
       <c r="E11" s="10"/>
@@ -19571,9 +22382,9 @@
       <c r="A12" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B12" s="18">
+      <c r="B12" s="18" t="str">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>4</v>
+        <v/>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -20433,11 +23244,11 @@
       <c r="F53" s="3"/>
       <c r="G53" s="3">
         <f>SUM(G3:G52)</f>
-        <v>47.8</v>
+        <v>200.38</v>
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0</v>
+        <v>9.11</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
@@ -20473,1338 +23284,4 @@
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B8F9EBE-D214-44A2-8A19-768E491F391C}">
-  <sheetPr>
-    <tabColor rgb="FF92D050"/>
-  </sheetPr>
-  <dimension ref="A1:Z53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="25.7109375" customWidth="1"/>
-    <col min="2" max="2" width="40.7109375" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" customWidth="1"/>
-    <col min="4" max="5" width="12.7109375" customWidth="1"/>
-    <col min="6" max="9" width="10.7109375" customWidth="1"/>
-    <col min="10" max="10" width="8.7109375" customWidth="1"/>
-    <col min="11" max="14" width="10.7109375" customWidth="1"/>
-    <col min="15" max="15" width="12.7109375" customWidth="1"/>
-    <col min="16" max="17" width="10.7109375" customWidth="1"/>
-    <col min="18" max="23" width="8.7109375" customWidth="1"/>
-    <col min="24" max="24" width="12.7109375" style="13" customWidth="1"/>
-    <col min="25" max="25" width="10.7109375" style="13" customWidth="1"/>
-    <col min="26" max="26" width="10.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D1" s="34" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="35"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="35"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="34" t="s">
-        <v>26</v>
-      </c>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="36"/>
-      <c r="X1" s="34"/>
-      <c r="Y1" s="35"/>
-      <c r="Z1" s="36"/>
-    </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="F2" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="G2" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="9"/>
-      <c r="K2" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="L2" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="M2" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="N2" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="O2" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="P2" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q2" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="X2" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y2" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z2" s="11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="D3" s="6">
-        <v>46086</v>
-      </c>
-      <c r="E3" s="6">
-        <v>46086</v>
-      </c>
-      <c r="F3" s="18">
-        <f t="shared" ref="F3:F52" si="0">IF(E3&gt;0,E3-D3,"")</f>
-        <v>0</v>
-      </c>
-      <c r="G3" s="3">
-        <v>10.86</v>
-      </c>
-      <c r="H3" s="3">
-        <v>0</v>
-      </c>
-      <c r="I3" s="3">
-        <v>0</v>
-      </c>
-      <c r="J3" s="13"/>
-      <c r="K3" s="3">
-        <f>G53</f>
-        <v>198.85</v>
-      </c>
-      <c r="L3" s="3">
-        <f>H53</f>
-        <v>8.85</v>
-      </c>
-      <c r="M3" s="3">
-        <f>I53</f>
-        <v>0</v>
-      </c>
-      <c r="N3" s="7">
-        <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
-        <v>0.10662775635719302</v>
-      </c>
-      <c r="O3" s="6">
-        <f>IF(B16=K3,MAX(E:E),"")</f>
-        <v>46239</v>
-      </c>
-      <c r="P3" s="2" t="str">
-        <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
-        <v/>
-      </c>
-      <c r="Q3" s="2">
-        <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
-        <v>0</v>
-      </c>
-      <c r="T3" s="15"/>
-      <c r="X3" s="6">
-        <f>B9</f>
-        <v>46058</v>
-      </c>
-      <c r="Y3" s="3">
-        <f>B16*-1</f>
-        <v>-198.85</v>
-      </c>
-      <c r="Z3" s="2" t="str">
-        <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="D4" s="6">
-        <v>46118</v>
-      </c>
-      <c r="E4" s="6">
-        <v>46118</v>
-      </c>
-      <c r="F4" s="18">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G4" s="2">
-        <v>10.76</v>
-      </c>
-      <c r="H4" s="3">
-        <v>0</v>
-      </c>
-      <c r="I4" s="3">
-        <v>0</v>
-      </c>
-      <c r="J4" s="9"/>
-      <c r="X4" s="6">
-        <f>E3</f>
-        <v>46086</v>
-      </c>
-      <c r="Y4" s="3">
-        <f>G3+H3-I3</f>
-        <v>10.86</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A5" s="5"/>
-      <c r="B5" s="6"/>
-      <c r="D5" s="6">
-        <v>46147</v>
-      </c>
-      <c r="E5" s="6">
-        <v>46147</v>
-      </c>
-      <c r="F5" s="18">
-        <v>0</v>
-      </c>
-      <c r="G5" s="2">
-        <v>10.96</v>
-      </c>
-      <c r="H5" s="3">
-        <v>0</v>
-      </c>
-      <c r="I5" s="3">
-        <v>0</v>
-      </c>
-      <c r="J5" s="9"/>
-      <c r="X5" s="6">
-        <f t="shared" ref="X5:X52" si="1">E4</f>
-        <v>46118</v>
-      </c>
-      <c r="Y5" s="3">
-        <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
-        <v>10.76</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A6" s="5"/>
-      <c r="B6" s="6"/>
-      <c r="D6" s="6">
-        <v>46178</v>
-      </c>
-      <c r="E6" s="6">
-        <v>46178</v>
-      </c>
-      <c r="F6" s="18">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G6" s="2">
-        <v>10.76</v>
-      </c>
-      <c r="H6" s="3">
-        <v>0</v>
-      </c>
-      <c r="I6" s="3">
-        <v>0</v>
-      </c>
-      <c r="J6" s="9"/>
-      <c r="X6" s="6">
-        <f t="shared" si="1"/>
-        <v>46147</v>
-      </c>
-      <c r="Y6" s="3">
-        <f t="shared" si="2"/>
-        <v>10.96</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A7" s="5"/>
-      <c r="B7" s="6"/>
-      <c r="D7" s="6">
-        <v>46209</v>
-      </c>
-      <c r="E7" s="6">
-        <v>46209</v>
-      </c>
-      <c r="F7" s="18">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G7" s="2">
-        <v>10.76</v>
-      </c>
-      <c r="H7" s="3">
-        <v>0</v>
-      </c>
-      <c r="I7" s="3">
-        <v>0</v>
-      </c>
-      <c r="J7" s="13"/>
-      <c r="X7" s="6">
-        <f t="shared" si="1"/>
-        <v>46178</v>
-      </c>
-      <c r="Y7" s="3">
-        <f t="shared" si="2"/>
-        <v>10.76</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="6" t="str">
-        <f>DATEDIF(B9,B11,"y") &amp; " m. " &amp; DATEDIF(B9,B11,"ym") &amp; " mėn. " &amp; DATEDIF(B9,B11,"md") &amp; " d."</f>
-        <v>0 m. 6 mėn. 0 d.</v>
-      </c>
-      <c r="D8" s="6">
-        <v>46239</v>
-      </c>
-      <c r="E8" s="6">
-        <v>46239</v>
-      </c>
-      <c r="F8" s="18">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G8" s="2">
-        <v>144.75</v>
-      </c>
-      <c r="H8" s="3">
-        <v>8.85</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="9"/>
-      <c r="X8" s="6">
-        <f t="shared" si="1"/>
-        <v>46209</v>
-      </c>
-      <c r="Y8" s="3">
-        <f t="shared" si="2"/>
-        <v>10.76</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="6">
-        <v>46058</v>
-      </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="13"/>
-      <c r="X9" s="6">
-        <f t="shared" si="1"/>
-        <v>46239</v>
-      </c>
-      <c r="Y9" s="3">
-        <f t="shared" si="2"/>
-        <v>153.6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" s="6">
-        <v>46070</v>
-      </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="13"/>
-      <c r="X10" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y10" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <v>46239</v>
-      </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G11" s="3"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="13"/>
-      <c r="X11" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y11" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" s="18" t="str">
-        <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v/>
-      </c>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G12" s="3"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="13"/>
-      <c r="X12" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y12" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A13" s="5"/>
-      <c r="B13" s="3"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="13"/>
-      <c r="N13" s="15"/>
-      <c r="X13" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y13" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="19"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="13"/>
-      <c r="X14" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" s="10"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="17"/>
-      <c r="L15" s="17"/>
-      <c r="M15" s="17"/>
-      <c r="N15" s="17"/>
-      <c r="O15" s="17"/>
-      <c r="P15" s="17"/>
-      <c r="Q15" s="17"/>
-      <c r="X15" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y15" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" s="3">
-        <v>198.85</v>
-      </c>
-      <c r="D16" s="10"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="13"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="20"/>
-      <c r="O16" s="21"/>
-      <c r="P16" s="13"/>
-      <c r="Q16" s="13"/>
-      <c r="X16" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y16" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D17" s="10"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="13"/>
-      <c r="X17" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y17" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D18" s="10"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="13"/>
-      <c r="X18" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y18" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D19" s="10"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="13"/>
-      <c r="X19" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y19" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D20" s="10"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="13"/>
-      <c r="X20" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y20" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D21" s="10"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="13"/>
-      <c r="X21" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y21" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D22" s="10"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="13"/>
-      <c r="X22" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y22" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D23" s="10"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="13"/>
-      <c r="X23" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y23" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D24" s="10"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="13"/>
-      <c r="X24" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y24" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D25" s="10"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="13"/>
-      <c r="X25" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y25" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D26" s="10"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="13"/>
-      <c r="X26" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y26" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D27" s="10"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="13"/>
-      <c r="X27" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y27" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D28" s="10"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="13"/>
-      <c r="X28" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y28" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D29" s="10"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="13"/>
-      <c r="X29" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y29" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D30" s="10"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="13"/>
-      <c r="X30" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y30" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D31" s="10"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="13"/>
-      <c r="X31" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y31" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D32" s="10"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="13"/>
-      <c r="X32" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y32" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D33" s="10"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="13"/>
-      <c r="X33" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y33" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D34" s="10"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="13"/>
-      <c r="X34" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y34" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D35" s="10"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="13"/>
-      <c r="X35" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y35" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D36" s="10"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="13"/>
-      <c r="X36" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y36" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D37" s="10"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
-      <c r="J37" s="13"/>
-      <c r="X37" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y37" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D38" s="10"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="13"/>
-      <c r="X38" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y38" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D39" s="10"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
-      <c r="J39" s="13"/>
-      <c r="X39" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y39" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D40" s="10"/>
-      <c r="E40" s="6"/>
-      <c r="F40" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
-      <c r="J40" s="13"/>
-      <c r="X40" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y40" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D41" s="10"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
-      <c r="J41" s="13"/>
-      <c r="X41" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y41" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D42" s="10"/>
-      <c r="E42" s="6"/>
-      <c r="F42" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G42" s="2"/>
-      <c r="H42" s="2"/>
-      <c r="I42" s="2"/>
-      <c r="J42" s="13"/>
-      <c r="X42" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y42" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D43" s="10"/>
-      <c r="E43" s="6"/>
-      <c r="F43" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G43" s="2"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
-      <c r="J43" s="13"/>
-      <c r="X43" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y43" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D44" s="10"/>
-      <c r="E44" s="6"/>
-      <c r="F44" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
-      <c r="I44" s="2"/>
-      <c r="J44" s="13"/>
-      <c r="X44" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y44" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D45" s="10"/>
-      <c r="E45" s="6"/>
-      <c r="F45" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
-      <c r="J45" s="13"/>
-      <c r="X45" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y45" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D46" s="10"/>
-      <c r="E46" s="6"/>
-      <c r="F46" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
-      <c r="J46" s="13"/>
-      <c r="X46" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y46" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D47" s="10"/>
-      <c r="E47" s="6"/>
-      <c r="F47" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="2"/>
-      <c r="J47" s="13"/>
-      <c r="X47" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y47" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D48" s="10"/>
-      <c r="E48" s="6"/>
-      <c r="F48" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
-      <c r="J48" s="13"/>
-      <c r="X48" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y48" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D49" s="10"/>
-      <c r="E49" s="6"/>
-      <c r="F49" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="2"/>
-      <c r="J49" s="13"/>
-      <c r="X49" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y49" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D50" s="10"/>
-      <c r="E50" s="6"/>
-      <c r="F50" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
-      <c r="J50" s="13"/>
-      <c r="X50" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y50" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D51" s="10"/>
-      <c r="E51" s="6"/>
-      <c r="F51" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
-      <c r="J51" s="13"/>
-      <c r="X51" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y51" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D52" s="10"/>
-      <c r="E52" s="6"/>
-      <c r="F52" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
-      <c r="J52" s="9"/>
-      <c r="X52" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y52" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D53" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E53" s="14"/>
-      <c r="F53" s="3"/>
-      <c r="G53" s="3">
-        <f>SUM(G3:G52)</f>
-        <v>198.85</v>
-      </c>
-      <c r="H53" s="3">
-        <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>8.85</v>
-      </c>
-      <c r="I53" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="D1:F1"/>
-    <mergeCell ref="G1:I1"/>
-    <mergeCell ref="K1:Q1"/>
-    <mergeCell ref="X1:Z1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="27" priority="1">
-      <formula>$Z$3="+"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="26" priority="2">
-      <formula>$B$16=$K$3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P3">
-    <cfRule type="expression" dxfId="25" priority="9">
-      <formula>$Z$3="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z3">
-    <cfRule type="expression" dxfId="24" priority="10">
-      <formula>$Z$3="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
 </file>
--- a/excel/Scramble Rima.xlsx
+++ b/excel/Scramble Rima.xlsx
@@ -1,34 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.08.08\Scramble\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Investavimas 2026.08.08\Scramble\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58445338-A6D7-4F26-92C0-17E4E6E2AEC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAA3BF51-FC74-4782-AE80-9E02F422BC09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
     <sheet name="Pinigai" sheetId="15" r:id="rId2"/>
-    <sheet name="September 2026" sheetId="37" r:id="rId3"/>
-    <sheet name="August 2026" sheetId="36" r:id="rId4"/>
-    <sheet name="July 2026" sheetId="35" r:id="rId5"/>
-    <sheet name="June 2026" sheetId="34" r:id="rId6"/>
-    <sheet name="May 2026" sheetId="33" r:id="rId7"/>
-    <sheet name="April 2026" sheetId="32" r:id="rId8"/>
-    <sheet name="March 2026" sheetId="31" r:id="rId9"/>
-    <sheet name="February 2026" sheetId="30" r:id="rId10"/>
-    <sheet name="January 2026" sheetId="29" r:id="rId11"/>
-    <sheet name="December 2025" sheetId="28" r:id="rId12"/>
-    <sheet name="November 2025" sheetId="27" r:id="rId13"/>
-    <sheet name="October 2025" sheetId="26" r:id="rId14"/>
-    <sheet name="September 2025" sheetId="25" r:id="rId15"/>
-    <sheet name="August 2025" sheetId="14" r:id="rId16"/>
+    <sheet name="October 2026" sheetId="38" r:id="rId3"/>
+    <sheet name="September 2026" sheetId="37" r:id="rId4"/>
+    <sheet name="August 2026" sheetId="36" r:id="rId5"/>
+    <sheet name="July 2026" sheetId="35" r:id="rId6"/>
+    <sheet name="June 2026" sheetId="34" r:id="rId7"/>
+    <sheet name="May 2026" sheetId="33" r:id="rId8"/>
+    <sheet name="April 2026" sheetId="32" r:id="rId9"/>
+    <sheet name="March 2026" sheetId="31" r:id="rId10"/>
+    <sheet name="February 2026" sheetId="30" r:id="rId11"/>
+    <sheet name="January 2026" sheetId="29" r:id="rId12"/>
+    <sheet name="December 2025" sheetId="28" r:id="rId13"/>
+    <sheet name="November 2025" sheetId="27" r:id="rId14"/>
+    <sheet name="October 2025" sheetId="26" r:id="rId15"/>
+    <sheet name="September 2025" sheetId="25" r:id="rId16"/>
+    <sheet name="August 2025" sheetId="14" r:id="rId17"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -51,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="61">
   <si>
     <t>Paskola</t>
   </si>
@@ -232,6 +233,9 @@
   <si>
     <t>September 2026</t>
   </si>
+  <si>
+    <t>October 2026</t>
+  </si>
 </sst>
 </file>
 
@@ -374,7 +378,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -456,19 +460,7 @@
     <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -495,7 +487,35 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="60">
+  <dxfs count="64">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -950,7 +970,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C5B9A1C-BE8D-4AA8-B425-A2B3857AC890}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7B0F18B6-341D-4B59-AA50-C7A940218AA5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1006,7 +1026,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78E2DBBC-C5B2-4288-AC0A-95368A14A86A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BB14DA99-6B92-49A0-A498-AA9896FB5940}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1062,7 +1082,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B495DA4-2D50-43E7-92C9-52E679196A7D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78E2DBBC-C5B2-4288-AC0A-95368A14A86A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1118,7 +1138,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67D9ED54-8C5F-4763-A103-EA86015ECDEF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B495DA4-2D50-43E7-92C9-52E679196A7D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1174,6 +1194,62 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67D9ED54-8C5F-4763-A103-EA86015ECDEF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3619500"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>914400</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD13F6DB-3617-4E16-85C6-CE67C2928B61}"/>
             </a:ext>
           </a:extLst>
@@ -1209,7 +1285,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1286,7 +1362,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C92B417E-0E73-40BA-95CB-0B8A5F160456}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C5B9A1C-BE8D-4AA8-B425-A2B3857AC890}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1342,7 +1418,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D26DB4C-231C-4C87-87A9-E78886E7807B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C92B417E-0E73-40BA-95CB-0B8A5F160456}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1398,7 +1474,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13F58B75-E6DB-4D82-A45E-AB511FF3C881}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D26DB4C-231C-4C87-87A9-E78886E7807B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1454,7 +1530,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75ADCD55-EE0C-46E9-9BA6-6DDCE4741191}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13F58B75-E6DB-4D82-A45E-AB511FF3C881}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1510,7 +1586,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4516F9B9-44DD-4606-BEE5-CB1D2AAA0AF1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75ADCD55-EE0C-46E9-9BA6-6DDCE4741191}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1566,7 +1642,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2810C3BC-F093-4506-BBA0-6D497E73A3C1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4516F9B9-44DD-4606-BEE5-CB1D2AAA0AF1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1622,7 +1698,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D2C6C96-E314-400B-9CB5-8B0597A3C6F1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2810C3BC-F093-4506-BBA0-6D497E73A3C1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1678,7 +1754,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BB14DA99-6B92-49A0-A498-AA9896FB5940}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D2C6C96-E314-400B-9CB5-8B0597A3C6F1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1994,43 +2070,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="36" t="s">
+      <c r="A1" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="38"/>
-      <c r="M1" s="39" t="s">
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="N1" s="39"/>
-      <c r="O1" s="39"/>
-      <c r="Q1" s="40" t="s">
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="Q1" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="R1" s="41"/>
-      <c r="S1" s="41"/>
-      <c r="T1" s="42"/>
-      <c r="U1" s="40" t="s">
+      <c r="R1" s="37"/>
+      <c r="S1" s="37"/>
+      <c r="T1" s="38"/>
+      <c r="U1" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="42"/>
-      <c r="W1" s="36" t="s">
+      <c r="V1" s="38"/>
+      <c r="W1" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="X1" s="37"/>
-      <c r="Y1" s="37"/>
-      <c r="Z1" s="38"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="33"/>
+      <c r="Z1" s="34"/>
       <c r="AA1" s="4" t="s">
         <v>27</v>
       </c>
@@ -2149,7 +2225,7 @@
       </c>
       <c r="H3" s="3">
         <f>'August 2025'!B16</f>
-        <v>220</v>
+        <v>110</v>
       </c>
       <c r="I3" s="6">
         <f>'August 2025'!B11</f>
@@ -2169,11 +2245,11 @@
       </c>
       <c r="M3" s="3">
         <f>'August 2025'!K3</f>
-        <v>220</v>
+        <v>110</v>
       </c>
       <c r="N3" s="3">
         <f>'August 2025'!L3</f>
-        <v>10.32</v>
+        <v>5.16</v>
       </c>
       <c r="O3" s="3">
         <f>'August 2025'!M3</f>
@@ -2182,43 +2258,43 @@
       <c r="P3" s="9"/>
       <c r="Q3" s="27">
         <f>Pinigai!I2</f>
-        <v>610</v>
+        <v>305</v>
       </c>
       <c r="R3" s="28">
         <f>SUM(H3:H98)-U3</f>
-        <v>687.56999999999971</v>
+        <v>348.42999999999995</v>
       </c>
       <c r="S3" s="27">
         <f>Pinigai!H2</f>
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="T3" s="27">
         <f>W3-R3</f>
-        <v>2.0000000000322871E-2</v>
+        <v>-2.9999999999972715E-2</v>
       </c>
       <c r="U3" s="28">
         <f>SUM(M3:M98)</f>
-        <v>1291.17</v>
+        <v>737.0200000000001</v>
       </c>
       <c r="V3" s="28">
         <f>SUM(N3:N98)-AA3</f>
-        <v>53.589999999999996</v>
+        <v>31.399999999999995</v>
       </c>
       <c r="W3" s="27">
         <f>Q3+S3+V3</f>
-        <v>687.59</v>
+        <v>348.4</v>
       </c>
       <c r="X3" s="27">
         <f>W3-Q3</f>
-        <v>77.590000000000032</v>
+        <v>43.399999999999977</v>
       </c>
       <c r="Y3" s="29">
         <f>(W3-Q3)/Q3</f>
-        <v>0.12719672131147547</v>
+        <v>0.14229508196721305</v>
       </c>
       <c r="Z3" s="30">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>0.11770399212837221</v>
+        <v>0.12746891379356382</v>
       </c>
       <c r="AA3" s="27">
         <f>SUM(O3:O98)</f>
@@ -2259,7 +2335,7 @@
       </c>
       <c r="H4" s="3">
         <f>'September 2025'!B16</f>
-        <v>222.28</v>
+        <v>111.14</v>
       </c>
       <c r="I4" s="6">
         <f>'September 2025'!B11</f>
@@ -2279,11 +2355,11 @@
       </c>
       <c r="M4" s="3">
         <f>'September 2025'!K3</f>
-        <v>222.28000000000003</v>
+        <v>111.14000000000001</v>
       </c>
       <c r="N4" s="3">
         <f>'September 2025'!L3</f>
-        <v>10.15</v>
+        <v>5.07</v>
       </c>
       <c r="O4" s="3">
         <f>'September 2025'!M3</f>
@@ -2335,7 +2411,7 @@
       </c>
       <c r="H5" s="3">
         <f>'October 2025'!B16</f>
-        <v>226.42</v>
+        <v>113.21</v>
       </c>
       <c r="I5" s="6">
         <f>'October 2025'!B11</f>
@@ -2355,11 +2431,11 @@
       </c>
       <c r="M5" s="3">
         <f>'October 2025'!K3</f>
-        <v>226.42</v>
+        <v>113.21000000000001</v>
       </c>
       <c r="N5" s="3">
         <f>'October 2025'!L3</f>
-        <v>10.1</v>
+        <v>5.05</v>
       </c>
       <c r="O5" s="3">
         <f>'October 2025'!M3</f>
@@ -2401,7 +2477,7 @@
       </c>
       <c r="H6" s="3">
         <f>'November 2025'!B16</f>
-        <v>37.97</v>
+        <v>18.98</v>
       </c>
       <c r="I6" s="6">
         <f>'November 2025'!B11</f>
@@ -2421,11 +2497,11 @@
       </c>
       <c r="M6" s="3">
         <f>'November 2025'!K3</f>
-        <v>37.97</v>
+        <v>18.98</v>
       </c>
       <c r="N6" s="3">
         <f>'November 2025'!L3</f>
-        <v>1.64</v>
+        <v>0.82</v>
       </c>
       <c r="O6" s="3">
         <f>'November 2025'!M3</f>
@@ -2467,7 +2543,7 @@
       </c>
       <c r="H7" s="3">
         <f>'December 2025'!B16</f>
-        <v>37.92</v>
+        <v>18.96</v>
       </c>
       <c r="I7" s="6">
         <f>'December 2025'!B11</f>
@@ -2487,11 +2563,11 @@
       </c>
       <c r="M7" s="3">
         <f>'December 2025'!K3</f>
-        <v>37.92</v>
+        <v>18.96</v>
       </c>
       <c r="N7" s="3">
         <f>'December 2025'!L3</f>
-        <v>1.66</v>
+        <v>0.83</v>
       </c>
       <c r="O7" s="3">
         <f>'December 2025'!M3</f>
@@ -2533,7 +2609,7 @@
       </c>
       <c r="H8" s="3">
         <f>'January 2026'!B16</f>
-        <v>39.950000000000003</v>
+        <v>19.98</v>
       </c>
       <c r="I8" s="6">
         <f>'January 2026'!B11</f>
@@ -2553,11 +2629,11 @@
       </c>
       <c r="M8" s="3">
         <f>'January 2026'!K3</f>
-        <v>39.949999999999996</v>
+        <v>19.98</v>
       </c>
       <c r="N8" s="3">
         <f>'January 2026'!L3</f>
-        <v>1.76</v>
+        <v>0.88</v>
       </c>
       <c r="O8" s="3">
         <f>'January 2026'!M3</f>
@@ -2599,7 +2675,7 @@
       </c>
       <c r="H9" s="3">
         <f>'February 2026'!B16</f>
-        <v>198.85</v>
+        <v>99.42</v>
       </c>
       <c r="I9" s="6">
         <f>'February 2026'!B11</f>
@@ -2619,11 +2695,11 @@
       </c>
       <c r="M9" s="3">
         <f>'February 2026'!K3</f>
-        <v>198.85</v>
+        <v>99.42</v>
       </c>
       <c r="N9" s="3">
         <f>'February 2026'!L3</f>
-        <v>8.85</v>
+        <v>4.42</v>
       </c>
       <c r="O9" s="3">
         <f>'February 2026'!M3</f>
@@ -2665,7 +2741,7 @@
       </c>
       <c r="H10" s="3">
         <f>'March 2026'!B16</f>
-        <v>200.38</v>
+        <v>100.19</v>
       </c>
       <c r="I10" s="6">
         <f>'March 2026'!B11</f>
@@ -2685,11 +2761,11 @@
       </c>
       <c r="M10" s="3">
         <f>'March 2026'!K3</f>
-        <v>200.38</v>
+        <v>100.19</v>
       </c>
       <c r="N10" s="3">
         <f>'March 2026'!L3</f>
-        <v>9.11</v>
+        <v>4.5599999999999996</v>
       </c>
       <c r="O10" s="3">
         <f>'March 2026'!M3</f>
@@ -2731,19 +2807,19 @@
       </c>
       <c r="H11" s="3">
         <f>'April 2026'!B16</f>
-        <v>205.39</v>
+        <v>102.7</v>
       </c>
       <c r="I11" s="6">
         <f>'April 2026'!B11</f>
         <v>46300</v>
       </c>
-      <c r="J11" s="6" t="str">
+      <c r="J11" s="6">
         <f>'April 2026'!O3</f>
-        <v/>
-      </c>
-      <c r="K11" s="18">
+        <v>46300</v>
+      </c>
+      <c r="K11" s="18" t="str">
         <f ca="1">'April 2026'!B12</f>
-        <v>5</v>
+        <v/>
       </c>
       <c r="L11" s="18" t="str">
         <f ca="1">'April 2026'!P3</f>
@@ -2751,11 +2827,11 @@
       </c>
       <c r="M11" s="3">
         <f>'April 2026'!K3</f>
-        <v>54</v>
+        <v>102.7</v>
       </c>
       <c r="N11" s="3">
         <f>'April 2026'!L3</f>
-        <v>0</v>
+        <v>4.6100000000000003</v>
       </c>
       <c r="O11" s="3">
         <f>'April 2026'!M3</f>
@@ -2797,7 +2873,7 @@
       </c>
       <c r="H12" s="3">
         <f>'May 2026'!B16</f>
-        <v>65.53</v>
+        <v>32.770000000000003</v>
       </c>
       <c r="I12" s="6">
         <f>'May 2026'!B11</f>
@@ -2809,7 +2885,7 @@
       </c>
       <c r="K12" s="18">
         <f ca="1">'May 2026'!B12</f>
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="L12" s="18" t="str">
         <f ca="1">'May 2026'!P3</f>
@@ -2817,7 +2893,7 @@
       </c>
       <c r="M12" s="3">
         <f>'May 2026'!K3</f>
-        <v>24.52</v>
+        <v>15.3</v>
       </c>
       <c r="N12" s="3">
         <f>'May 2026'!L3</f>
@@ -2862,7 +2938,7 @@
       </c>
       <c r="H13" s="3">
         <f>'June 2026'!B16</f>
-        <v>69.010000000000005</v>
+        <v>34.5</v>
       </c>
       <c r="I13" s="6">
         <f>'June 2026'!B11</f>
@@ -2874,7 +2950,7 @@
       </c>
       <c r="K13" s="18">
         <f ca="1">'June 2026'!B12</f>
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="L13" s="18" t="str">
         <f ca="1">'June 2026'!P3</f>
@@ -2882,7 +2958,7 @@
       </c>
       <c r="M13" s="3">
         <f>'June 2026'!K3</f>
-        <v>12.419999999999998</v>
+        <v>8.2799999999999994</v>
       </c>
       <c r="N13" s="3">
         <f>'June 2026'!L3</f>
@@ -2927,7 +3003,7 @@
       </c>
       <c r="H14" s="3">
         <f>'July 2026'!B16</f>
-        <v>71.86</v>
+        <v>35.93</v>
       </c>
       <c r="I14" s="6">
         <f>'July 2026'!B11</f>
@@ -2939,7 +3015,7 @@
       </c>
       <c r="K14" s="18">
         <f ca="1">'July 2026'!B12</f>
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="L14" s="18" t="str">
         <f ca="1">'July 2026'!P3</f>
@@ -2947,7 +3023,7 @@
       </c>
       <c r="M14" s="3">
         <f>'July 2026'!K3</f>
-        <v>3.44</v>
+        <v>2.58</v>
       </c>
       <c r="N14" s="3">
         <f>'July 2026'!L3</f>
@@ -2992,7 +3068,7 @@
       </c>
       <c r="H15" s="3">
         <f>'August 2026'!B16</f>
-        <v>185.68</v>
+        <v>92.84</v>
       </c>
       <c r="I15" s="6">
         <f>'August 2026'!B11</f>
@@ -3004,7 +3080,7 @@
       </c>
       <c r="K15" s="18">
         <f ca="1">'August 2026'!B12</f>
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="L15" s="18" t="str">
         <f ca="1">'August 2026'!P3</f>
@@ -3057,7 +3133,7 @@
       </c>
       <c r="H16" s="3">
         <f>'September 2026'!B16</f>
-        <v>197.5</v>
+        <v>98.75</v>
       </c>
       <c r="I16" s="6">
         <f>'September 2026'!B11</f>
@@ -3069,7 +3145,7 @@
       </c>
       <c r="K16" s="18">
         <f ca="1">'September 2026'!B12</f>
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="L16" s="18" t="str">
         <f ca="1">'September 2026'!P3</f>
@@ -3077,7 +3153,7 @@
       </c>
       <c r="M16" s="3">
         <f>'September 2026'!K3</f>
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="N16" s="3">
         <f>'September 2026'!L3</f>
@@ -3093,22 +3169,69 @@
       </c>
     </row>
     <row r="17" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A17" s="2"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="24"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="18"/>
-      <c r="L17" s="18"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="3"/>
-      <c r="AC17" s="1"/>
+      <c r="A17" s="2">
+        <v>15</v>
+      </c>
+      <c r="B17" s="6">
+        <f>'October 2026'!B9</f>
+        <v>46300</v>
+      </c>
+      <c r="C17" s="24" t="str">
+        <f>'October 2026'!B1</f>
+        <v>October 2026</v>
+      </c>
+      <c r="D17" s="2" t="str">
+        <f>'October 2026'!B2</f>
+        <v>Estonia</v>
+      </c>
+      <c r="E17" s="2" t="str">
+        <f>'October 2026'!B3</f>
+        <v>Scramble</v>
+      </c>
+      <c r="F17" s="2" t="str">
+        <f>'October 2026'!B8</f>
+        <v>0 m. 6 mėn. 0 d.</v>
+      </c>
+      <c r="G17" s="7" t="str">
+        <f>'October 2026'!B15</f>
+        <v>9-12%</v>
+      </c>
+      <c r="H17" s="3">
+        <f>'October 2026'!B16</f>
+        <v>96.08</v>
+      </c>
+      <c r="I17" s="6">
+        <f>'October 2026'!B11</f>
+        <v>46482</v>
+      </c>
+      <c r="J17" s="6" t="str">
+        <f>'October 2026'!O3</f>
+        <v/>
+      </c>
+      <c r="K17" s="18">
+        <f ca="1">'October 2026'!B12</f>
+        <v>175</v>
+      </c>
+      <c r="L17" s="18" t="str">
+        <f ca="1">'October 2026'!P3</f>
+        <v/>
+      </c>
+      <c r="M17" s="3">
+        <f>'October 2026'!K3</f>
+        <v>0</v>
+      </c>
+      <c r="N17" s="3">
+        <f>'October 2026'!L3</f>
+        <v>0</v>
+      </c>
+      <c r="O17" s="3">
+        <f>'October 2026'!M3</f>
+        <v>0</v>
+      </c>
+      <c r="AC17" s="3" t="str">
+        <f ca="1">'October 2026'!Z3</f>
+        <v/>
+      </c>
     </row>
     <row r="18" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
@@ -3264,20 +3387,20 @@
     <mergeCell ref="U1:V1"/>
   </mergeCells>
   <conditionalFormatting sqref="A3:O25">
-    <cfRule type="expression" dxfId="59" priority="9">
+    <cfRule type="expression" dxfId="63" priority="9">
       <formula>$AC3="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="58" priority="13">
+    <cfRule type="expression" dxfId="62" priority="13">
       <formula>AND($H3&gt;0,$H3=$M3)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC3:AC25">
-    <cfRule type="expression" dxfId="57" priority="2">
+    <cfRule type="expression" dxfId="61" priority="2">
       <formula>AND($H3&gt;0,$H3=$M3)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC6:AC16">
-    <cfRule type="expression" dxfId="56" priority="1">
+  <conditionalFormatting sqref="AC6:AC17">
+    <cfRule type="expression" dxfId="60" priority="1">
       <formula>$AC6="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3296,6 +3419,7 @@
     <hyperlink ref="C14" location="'July 2026'!A1" display="'July 2026'!A1" xr:uid="{8B58AC79-8F19-4849-BA55-1D38985B2EEB}"/>
     <hyperlink ref="C15" location="'August 2026'!A1" display="'August 2026'!A1" xr:uid="{6EA87317-B9C8-43E4-8AE8-6D1BF358572F}"/>
     <hyperlink ref="C16" location="'September 2026'!A1" display="'September 2026'!A1" xr:uid="{76FDE0B3-A187-4C19-82A3-3B813BD03F8C}"/>
+    <hyperlink ref="C17" location="'September 2026'!A1" display="'September 2026'!A1" xr:uid="{6A82B495-20C1-4703-AAAE-64DBBA9A993B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3303,6 +3427,1341 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29B83440-5743-4944-A92C-7C00476AA6BD}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
+  <dimension ref="A1:Z53"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="40.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="9" width="10.7109375" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" customWidth="1"/>
+    <col min="11" max="14" width="10.7109375" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" customWidth="1"/>
+    <col min="16" max="17" width="10.7109375" customWidth="1"/>
+    <col min="18" max="23" width="8.7109375" customWidth="1"/>
+    <col min="24" max="24" width="12.7109375" style="13" customWidth="1"/>
+    <col min="25" max="25" width="10.7109375" style="13" customWidth="1"/>
+    <col min="26" max="26" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="33"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="33"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
+      <c r="Q1" s="34"/>
+      <c r="X1" s="32"/>
+      <c r="Y1" s="33"/>
+      <c r="Z1" s="34"/>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="9"/>
+      <c r="K2" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O2" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="P2" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q2" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="X2" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y2" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z2" s="11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" s="6">
+        <v>46118</v>
+      </c>
+      <c r="E3" s="6">
+        <v>46118</v>
+      </c>
+      <c r="F3" s="18">
+        <f t="shared" ref="F3:F52" si="0">IF(E3&gt;0,E3-D3,"")</f>
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>4.8099999999999996</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0</v>
+      </c>
+      <c r="J3" s="13"/>
+      <c r="K3" s="3">
+        <f>G53</f>
+        <v>100.19</v>
+      </c>
+      <c r="L3" s="3">
+        <f>H53</f>
+        <v>4.5599999999999996</v>
+      </c>
+      <c r="M3" s="3">
+        <f>I53</f>
+        <v>0</v>
+      </c>
+      <c r="N3" s="7">
+        <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
+        <v>0.1039698302745819</v>
+      </c>
+      <c r="O3" s="6">
+        <f>IF(B16=K3,MAX(E:E),"")</f>
+        <v>46272</v>
+      </c>
+      <c r="P3" s="2" t="str">
+        <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
+        <v/>
+      </c>
+      <c r="Q3" s="2">
+        <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
+        <v>0</v>
+      </c>
+      <c r="T3" s="15"/>
+      <c r="X3" s="6">
+        <f>B9</f>
+        <v>46086</v>
+      </c>
+      <c r="Y3" s="3">
+        <f>B16*-1</f>
+        <v>-100.19</v>
+      </c>
+      <c r="Z3" s="2" t="str">
+        <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="6">
+        <v>46147</v>
+      </c>
+      <c r="E4" s="6">
+        <v>46147</v>
+      </c>
+      <c r="F4" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="2">
+        <v>4.8099999999999996</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3">
+        <v>0</v>
+      </c>
+      <c r="J4" s="9"/>
+      <c r="X4" s="6">
+        <f>E3</f>
+        <v>46118</v>
+      </c>
+      <c r="Y4" s="3">
+        <f>G3+H3-I3</f>
+        <v>4.8099999999999996</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A5" s="5"/>
+      <c r="B5" s="6"/>
+      <c r="D5" s="6">
+        <v>46178</v>
+      </c>
+      <c r="E5" s="6">
+        <v>46178</v>
+      </c>
+      <c r="F5" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G5" s="2">
+        <v>4.8099999999999996</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3">
+        <v>0</v>
+      </c>
+      <c r="J5" s="9"/>
+      <c r="X5" s="6">
+        <f t="shared" ref="X5:X52" si="1">E4</f>
+        <v>46147</v>
+      </c>
+      <c r="Y5" s="3">
+        <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
+        <v>4.8099999999999996</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A6" s="5"/>
+      <c r="B6" s="6"/>
+      <c r="D6" s="6">
+        <v>46209</v>
+      </c>
+      <c r="E6" s="6">
+        <v>46209</v>
+      </c>
+      <c r="F6" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="2">
+        <v>4.8099999999999996</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3">
+        <v>0</v>
+      </c>
+      <c r="J6" s="9"/>
+      <c r="X6" s="6">
+        <f t="shared" si="1"/>
+        <v>46178</v>
+      </c>
+      <c r="Y6" s="3">
+        <f t="shared" si="2"/>
+        <v>4.8099999999999996</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A7" s="5"/>
+      <c r="B7" s="6"/>
+      <c r="D7" s="6">
+        <v>46239</v>
+      </c>
+      <c r="E7" s="6">
+        <v>46239</v>
+      </c>
+      <c r="F7" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>4.66</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3">
+        <v>0</v>
+      </c>
+      <c r="J7" s="13"/>
+      <c r="X7" s="6">
+        <f t="shared" si="1"/>
+        <v>46209</v>
+      </c>
+      <c r="Y7" s="3">
+        <f t="shared" si="2"/>
+        <v>4.8099999999999996</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="6" t="str">
+        <f>DATEDIF(B9,B11,"y") &amp; " m. " &amp; DATEDIF(B9,B11,"ym") &amp; " mėn. " &amp; DATEDIF(B9,B11,"md") &amp; " d."</f>
+        <v>0 m. 6 mėn. 2 d.</v>
+      </c>
+      <c r="D8" s="6">
+        <v>46272</v>
+      </c>
+      <c r="E8" s="6">
+        <v>46272</v>
+      </c>
+      <c r="F8" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G8" s="2">
+        <v>76.290000000000006</v>
+      </c>
+      <c r="H8" s="3">
+        <v>4.5599999999999996</v>
+      </c>
+      <c r="I8" s="3">
+        <v>0</v>
+      </c>
+      <c r="J8" s="9"/>
+      <c r="X8" s="6">
+        <f t="shared" si="1"/>
+        <v>46239</v>
+      </c>
+      <c r="Y8" s="3">
+        <f t="shared" si="2"/>
+        <v>4.66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="6">
+        <v>46086</v>
+      </c>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G9" s="2"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="13"/>
+      <c r="X9" s="6">
+        <f t="shared" si="1"/>
+        <v>46272</v>
+      </c>
+      <c r="Y9" s="3">
+        <f t="shared" si="2"/>
+        <v>80.850000000000009</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="6">
+        <v>46098</v>
+      </c>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="13"/>
+      <c r="X10" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y10" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <v>46272</v>
+      </c>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G11" s="3"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="13"/>
+      <c r="X11" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y11" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="18" t="str">
+        <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G12" s="3"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="13"/>
+      <c r="X12" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y12" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A13" s="5"/>
+      <c r="B13" s="3"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="13"/>
+      <c r="N13" s="15"/>
+      <c r="X13" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="19"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="13"/>
+      <c r="X14" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="10"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="17"/>
+      <c r="M15" s="17"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="17"/>
+      <c r="X15" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="3">
+        <v>100.19</v>
+      </c>
+      <c r="D16" s="10"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="21"/>
+      <c r="P16" s="13"/>
+      <c r="Q16" s="13"/>
+      <c r="X16" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y16" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D17" s="10"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="13"/>
+      <c r="X17" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y17" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D18" s="10"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="13"/>
+      <c r="X18" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y18" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D19" s="10"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="13"/>
+      <c r="X19" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y19" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D20" s="10"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="13"/>
+      <c r="X20" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D21" s="10"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="13"/>
+      <c r="X21" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y21" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D22" s="10"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="13"/>
+      <c r="X22" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D23" s="10"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="13"/>
+      <c r="X23" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y23" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D24" s="10"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="13"/>
+      <c r="X24" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D25" s="10"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="13"/>
+      <c r="X25" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D26" s="10"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="13"/>
+      <c r="X26" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y26" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D27" s="10"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="13"/>
+      <c r="X27" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y27" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D28" s="10"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="13"/>
+      <c r="X28" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D29" s="10"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="13"/>
+      <c r="X29" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D30" s="10"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="13"/>
+      <c r="X30" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D31" s="10"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="13"/>
+      <c r="X31" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D32" s="10"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="13"/>
+      <c r="X32" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D33" s="10"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="13"/>
+      <c r="X33" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y33" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D34" s="10"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="13"/>
+      <c r="X34" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D35" s="10"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="13"/>
+      <c r="X35" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y35" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D36" s="10"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="13"/>
+      <c r="X36" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y36" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D37" s="10"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="13"/>
+      <c r="X37" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y37" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D38" s="10"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="13"/>
+      <c r="X38" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y38" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D39" s="10"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="13"/>
+      <c r="X39" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y39" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D40" s="10"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="13"/>
+      <c r="X40" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y40" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D41" s="10"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="13"/>
+      <c r="X41" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y41" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D42" s="10"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="13"/>
+      <c r="X42" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D43" s="10"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="13"/>
+      <c r="X43" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y43" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D44" s="10"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="13"/>
+      <c r="X44" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y44" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D45" s="10"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="13"/>
+      <c r="X45" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y45" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D46" s="10"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="13"/>
+      <c r="X46" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y46" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D47" s="10"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="13"/>
+      <c r="X47" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D48" s="10"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="13"/>
+      <c r="X48" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y48" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D49" s="10"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="13"/>
+      <c r="X49" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y49" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D50" s="10"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="13"/>
+      <c r="X50" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D51" s="10"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="13"/>
+      <c r="X51" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D52" s="10"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="9"/>
+      <c r="X52" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y52" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D53" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E53" s="14"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3">
+        <f>SUM(G3:G52)</f>
+        <v>100.19</v>
+      </c>
+      <c r="H53" s="3">
+        <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
+        <v>4.5599999999999996</v>
+      </c>
+      <c r="I53" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="X1:Z1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="expression" dxfId="31" priority="1">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="2">
+      <formula>$B$16=$K$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P3">
+    <cfRule type="expression" dxfId="29" priority="7">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z3">
+    <cfRule type="expression" dxfId="28" priority="8">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B8F9EBE-D214-44A2-8A19-768E491F391C}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -3332,29 +4791,29 @@
       <c r="B1" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="D1" s="36" t="s">
+      <c r="D1" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="37"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="37"/>
-      <c r="I1" s="38"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="33"/>
+      <c r="I1" s="34"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="36" t="s">
+      <c r="K1" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
-      <c r="N1" s="37"/>
-      <c r="O1" s="37"/>
-      <c r="P1" s="37"/>
-      <c r="Q1" s="38"/>
-      <c r="X1" s="36"/>
-      <c r="Y1" s="37"/>
-      <c r="Z1" s="38"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
+      <c r="Q1" s="34"/>
+      <c r="X1" s="32"/>
+      <c r="Y1" s="33"/>
+      <c r="Z1" s="34"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -3431,7 +4890,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="3">
-        <v>10.86</v>
+        <v>5.43</v>
       </c>
       <c r="H3" s="3">
         <v>0</v>
@@ -3442,11 +4901,11 @@
       <c r="J3" s="13"/>
       <c r="K3" s="3">
         <f>G53</f>
-        <v>198.85</v>
+        <v>99.42</v>
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>8.85</v>
+        <v>4.42</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
@@ -3454,7 +4913,7 @@
       </c>
       <c r="N3" s="7">
         <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
-        <v>0.10662775635719302</v>
+        <v>0.10651074051856996</v>
       </c>
       <c r="O3" s="6">
         <f>IF(B16=K3,MAX(E:E),"")</f>
@@ -3475,7 +4934,7 @@
       </c>
       <c r="Y3" s="3">
         <f>B16*-1</f>
-        <v>-198.85</v>
+        <v>-99.42</v>
       </c>
       <c r="Z3" s="2" t="str">
         <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
@@ -3500,7 +4959,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="2">
-        <v>10.76</v>
+        <v>5.38</v>
       </c>
       <c r="H4" s="3">
         <v>0</v>
@@ -3515,7 +4974,7 @@
       </c>
       <c r="Y4" s="3">
         <f>G3+H3-I3</f>
-        <v>10.86</v>
+        <v>5.43</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
@@ -3531,7 +4990,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="2">
-        <v>10.96</v>
+        <v>5.48</v>
       </c>
       <c r="H5" s="3">
         <v>0</v>
@@ -3546,7 +5005,7 @@
       </c>
       <c r="Y5" s="3">
         <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
-        <v>10.76</v>
+        <v>5.38</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
@@ -3563,7 +5022,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="2">
-        <v>10.76</v>
+        <v>5.38</v>
       </c>
       <c r="H6" s="3">
         <v>0</v>
@@ -3578,7 +5037,7 @@
       </c>
       <c r="Y6" s="3">
         <f t="shared" si="2"/>
-        <v>10.96</v>
+        <v>5.48</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
@@ -3595,7 +5054,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="2">
-        <v>10.76</v>
+        <v>5.38</v>
       </c>
       <c r="H7" s="3">
         <v>0</v>
@@ -3610,7 +5069,7 @@
       </c>
       <c r="Y7" s="3">
         <f t="shared" si="2"/>
-        <v>10.76</v>
+        <v>5.38</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
@@ -3632,10 +5091,10 @@
         <v>0</v>
       </c>
       <c r="G8" s="2">
-        <v>144.75</v>
+        <v>72.37</v>
       </c>
       <c r="H8" s="3">
-        <v>8.85</v>
+        <v>4.42</v>
       </c>
       <c r="I8" s="3">
         <v>0</v>
@@ -3647,7 +5106,7 @@
       </c>
       <c r="Y8" s="3">
         <f t="shared" si="2"/>
-        <v>10.76</v>
+        <v>5.38</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
@@ -3673,7 +5132,7 @@
       </c>
       <c r="Y9" s="3">
         <f t="shared" si="2"/>
-        <v>153.6</v>
+        <v>76.790000000000006</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
@@ -3838,7 +5297,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="3">
-        <v>198.85</v>
+        <v>99.42</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="6"/>
@@ -4594,11 +6053,11 @@
       <c r="F53" s="3"/>
       <c r="G53" s="3">
         <f>SUM(G3:G52)</f>
-        <v>198.85</v>
+        <v>99.42</v>
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>8.85</v>
+        <v>4.42</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
@@ -4636,7 +6095,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E465F013-9FF2-44FD-828F-D999C3230D4E}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -4666,29 +6125,29 @@
       <c r="B1" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="36" t="s">
+      <c r="D1" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="37"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="37"/>
-      <c r="I1" s="38"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="33"/>
+      <c r="I1" s="34"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="36" t="s">
+      <c r="K1" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
-      <c r="N1" s="37"/>
-      <c r="O1" s="37"/>
-      <c r="P1" s="37"/>
-      <c r="Q1" s="38"/>
-      <c r="X1" s="36"/>
-      <c r="Y1" s="37"/>
-      <c r="Z1" s="38"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
+      <c r="Q1" s="34"/>
+      <c r="X1" s="32"/>
+      <c r="Y1" s="33"/>
+      <c r="Z1" s="34"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -4765,7 +6224,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="3">
-        <v>2.2599999999999998</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="H3" s="3">
         <v>0</v>
@@ -4776,11 +6235,11 @@
       <c r="J3" s="13"/>
       <c r="K3" s="3">
         <f>G53</f>
-        <v>39.949999999999996</v>
+        <v>19.98</v>
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>1.76</v>
+        <v>0.88</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
@@ -4788,7 +6247,7 @@
       </c>
       <c r="N3" s="7">
         <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
-        <v>0.10550422072410584</v>
+        <v>0.1054727613925934</v>
       </c>
       <c r="O3" s="6">
         <f>IF(B16=K3,MAX(E:E),"")</f>
@@ -4809,7 +6268,7 @@
       </c>
       <c r="Y3" s="3">
         <f>B16*-1</f>
-        <v>-39.950000000000003</v>
+        <v>-19.98</v>
       </c>
       <c r="Z3" s="2" t="str">
         <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
@@ -4834,7 +6293,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="2">
-        <v>2.2599999999999998</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="H4" s="3">
         <v>0</v>
@@ -4849,7 +6308,7 @@
       </c>
       <c r="Y4" s="3">
         <f>G3+H3-I3</f>
-        <v>2.2599999999999998</v>
+        <v>1.1299999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
@@ -4866,7 +6325,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="2">
-        <v>2.2599999999999998</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="H5" s="3">
         <v>0</v>
@@ -4881,7 +6340,7 @@
       </c>
       <c r="Y5" s="3">
         <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
-        <v>2.2599999999999998</v>
+        <v>1.1299999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
@@ -4898,7 +6357,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="2">
-        <v>2.2599999999999998</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="H6" s="3">
         <v>0</v>
@@ -4913,7 +6372,7 @@
       </c>
       <c r="Y6" s="3">
         <f t="shared" si="2"/>
-        <v>2.2599999999999998</v>
+        <v>1.1299999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
@@ -4930,7 +6389,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="2">
-        <v>2.2599999999999998</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="H7" s="3">
         <v>0</v>
@@ -4945,7 +6404,7 @@
       </c>
       <c r="Y7" s="3">
         <f t="shared" si="2"/>
-        <v>2.2599999999999998</v>
+        <v>1.1299999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
@@ -4967,10 +6426,10 @@
         <v>0</v>
       </c>
       <c r="G8" s="2">
-        <v>28.65</v>
+        <v>14.33</v>
       </c>
       <c r="H8" s="3">
-        <v>1.76</v>
+        <v>0.88</v>
       </c>
       <c r="I8" s="3">
         <v>0</v>
@@ -4982,7 +6441,7 @@
       </c>
       <c r="Y8" s="3">
         <f t="shared" si="2"/>
-        <v>2.2599999999999998</v>
+        <v>1.1299999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
@@ -5005,7 +6464,7 @@
       </c>
       <c r="Y9" s="3">
         <f t="shared" si="2"/>
-        <v>30.41</v>
+        <v>15.21</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
@@ -5170,7 +6629,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="3">
-        <v>39.950000000000003</v>
+        <v>19.98</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="6"/>
@@ -5926,11 +7385,11 @@
       <c r="F53" s="3"/>
       <c r="G53" s="3">
         <f>SUM(G3:G52)</f>
-        <v>39.949999999999996</v>
+        <v>19.98</v>
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>1.76</v>
+        <v>0.88</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
@@ -5968,7 +7427,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1D1CAB2-9974-4180-AFF6-5274525FE544}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -5998,29 +7457,29 @@
       <c r="B1" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="D1" s="36" t="s">
+      <c r="D1" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="37"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="37"/>
-      <c r="I1" s="38"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="33"/>
+      <c r="I1" s="34"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="36" t="s">
+      <c r="K1" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
-      <c r="N1" s="37"/>
-      <c r="O1" s="37"/>
-      <c r="P1" s="37"/>
-      <c r="Q1" s="38"/>
-      <c r="X1" s="36"/>
-      <c r="Y1" s="37"/>
-      <c r="Z1" s="38"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
+      <c r="Q1" s="34"/>
+      <c r="X1" s="32"/>
+      <c r="Y1" s="33"/>
+      <c r="Z1" s="34"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -6097,7 +7556,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="3">
-        <v>2.0299999999999998</v>
+        <v>1.01</v>
       </c>
       <c r="H3" s="3">
         <v>0</v>
@@ -6108,11 +7567,11 @@
       <c r="J3" s="13"/>
       <c r="K3" s="3">
         <f>G53</f>
-        <v>37.92</v>
+        <v>18.96</v>
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>1.66</v>
+        <v>0.83</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
@@ -6120,7 +7579,7 @@
       </c>
       <c r="N3" s="7">
         <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
-        <v>0.10373992323875425</v>
+        <v>0.10366029143333436</v>
       </c>
       <c r="O3" s="6">
         <f>IF(B16=K3,MAX(E:E),"")</f>
@@ -6141,7 +7600,7 @@
       </c>
       <c r="Y3" s="3">
         <f>B16*-1</f>
-        <v>-37.92</v>
+        <v>-18.96</v>
       </c>
       <c r="Z3" s="2" t="str">
         <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
@@ -6166,7 +7625,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="2">
-        <v>2.0299999999999998</v>
+        <v>1.01</v>
       </c>
       <c r="H4" s="3">
         <v>0</v>
@@ -6181,7 +7640,7 @@
       </c>
       <c r="Y4" s="3">
         <f>G3+H3-I3</f>
-        <v>2.0299999999999998</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
@@ -6198,7 +7657,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="2">
-        <v>2.0299999999999998</v>
+        <v>1.01</v>
       </c>
       <c r="H5" s="3">
         <v>0</v>
@@ -6213,7 +7672,7 @@
       </c>
       <c r="Y5" s="3">
         <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
-        <v>2.0299999999999998</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
@@ -6230,7 +7689,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="2">
-        <v>2.0299999999999998</v>
+        <v>1.01</v>
       </c>
       <c r="H6" s="3">
         <v>0</v>
@@ -6245,7 +7704,7 @@
       </c>
       <c r="Y6" s="3">
         <f t="shared" si="2"/>
-        <v>2.0299999999999998</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
@@ -6262,7 +7721,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="2">
-        <v>2.0299999999999998</v>
+        <v>1.01</v>
       </c>
       <c r="H7" s="3">
         <v>0</v>
@@ -6277,7 +7736,7 @@
       </c>
       <c r="Y7" s="3">
         <f t="shared" si="2"/>
-        <v>2.0299999999999998</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
@@ -6299,10 +7758,10 @@
         <v>0</v>
       </c>
       <c r="G8" s="2">
-        <v>27.77</v>
+        <v>13.91</v>
       </c>
       <c r="H8" s="3">
-        <v>1.66</v>
+        <v>0.83</v>
       </c>
       <c r="I8" s="3">
         <v>0</v>
@@ -6314,7 +7773,7 @@
       </c>
       <c r="Y8" s="3">
         <f t="shared" si="2"/>
-        <v>2.0299999999999998</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
@@ -6337,7 +7796,7 @@
       </c>
       <c r="Y9" s="3">
         <f t="shared" si="2"/>
-        <v>29.43</v>
+        <v>14.74</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
@@ -6496,7 +7955,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="3">
-        <v>37.92</v>
+        <v>18.96</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="6"/>
@@ -7252,11 +8711,11 @@
       <c r="F53" s="3"/>
       <c r="G53" s="3">
         <f>SUM(G3:G52)</f>
-        <v>37.92</v>
+        <v>18.96</v>
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>1.66</v>
+        <v>0.83</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
@@ -7294,7 +8753,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3754DA4B-78B4-44BD-BB4B-39C6D453FDD0}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -7324,29 +8783,29 @@
       <c r="B1" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="36" t="s">
+      <c r="D1" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="37"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="37"/>
-      <c r="I1" s="38"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="33"/>
+      <c r="I1" s="34"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="36" t="s">
+      <c r="K1" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
-      <c r="N1" s="37"/>
-      <c r="O1" s="37"/>
-      <c r="P1" s="37"/>
-      <c r="Q1" s="38"/>
-      <c r="X1" s="36"/>
-      <c r="Y1" s="37"/>
-      <c r="Z1" s="38"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
+      <c r="Q1" s="34"/>
+      <c r="X1" s="32"/>
+      <c r="Y1" s="33"/>
+      <c r="Z1" s="34"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -7423,7 +8882,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="3">
-        <v>1.95</v>
+        <v>0.98</v>
       </c>
       <c r="H3" s="3">
         <v>0</v>
@@ -7434,11 +8893,11 @@
       <c r="J3" s="13"/>
       <c r="K3" s="3">
         <f>G53</f>
-        <v>37.97</v>
+        <v>18.98</v>
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>1.64</v>
+        <v>0.82</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
@@ -7446,7 +8905,7 @@
       </c>
       <c r="N3" s="7">
         <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
-        <v>0.10221806168556213</v>
+        <v>0.10232736468315123</v>
       </c>
       <c r="O3" s="6">
         <f>IF(B16=K3,MAX(E:E),"")</f>
@@ -7467,7 +8926,7 @@
       </c>
       <c r="Y3" s="3">
         <f>B16*-1</f>
-        <v>-37.97</v>
+        <v>-18.98</v>
       </c>
       <c r="Z3" s="2" t="str">
         <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
@@ -7492,7 +8951,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="2">
-        <v>1.95</v>
+        <v>0.98</v>
       </c>
       <c r="H4" s="3">
         <v>0</v>
@@ -7507,7 +8966,7 @@
       </c>
       <c r="Y4" s="3">
         <f>G3+H3-I3</f>
-        <v>1.95</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
@@ -7524,7 +8983,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="2">
-        <v>1.95</v>
+        <v>0.98</v>
       </c>
       <c r="H5" s="3">
         <v>0</v>
@@ -7539,7 +8998,7 @@
       </c>
       <c r="Y5" s="3">
         <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
-        <v>1.95</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
@@ -7556,7 +9015,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="2">
-        <v>1.95</v>
+        <v>0.98</v>
       </c>
       <c r="H6" s="3">
         <v>0</v>
@@ -7571,7 +9030,7 @@
       </c>
       <c r="Y6" s="3">
         <f t="shared" si="2"/>
-        <v>1.95</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
@@ -7588,7 +9047,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="2">
-        <v>1.95</v>
+        <v>0.98</v>
       </c>
       <c r="H7" s="3">
         <v>0</v>
@@ -7603,7 +9062,7 @@
       </c>
       <c r="Y7" s="3">
         <f t="shared" si="2"/>
-        <v>1.95</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
@@ -7625,10 +9084,10 @@
         <v>0</v>
       </c>
       <c r="G8" s="2">
-        <v>28.22</v>
+        <v>14.08</v>
       </c>
       <c r="H8" s="3">
-        <v>1.64</v>
+        <v>0.82</v>
       </c>
       <c r="I8" s="3">
         <v>0</v>
@@ -7640,7 +9099,7 @@
       </c>
       <c r="Y8" s="3">
         <f t="shared" si="2"/>
-        <v>1.95</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
@@ -7663,7 +9122,7 @@
       </c>
       <c r="Y9" s="3">
         <f t="shared" si="2"/>
-        <v>29.86</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
@@ -7822,7 +9281,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="3">
-        <v>37.97</v>
+        <v>18.98</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="6"/>
@@ -8578,11 +10037,11 @@
       <c r="F53" s="3"/>
       <c r="G53" s="3">
         <f>SUM(G3:G52)</f>
-        <v>37.97</v>
+        <v>18.98</v>
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>1.64</v>
+        <v>0.82</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
@@ -8620,7 +10079,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A46497B-E391-4B8F-8947-28547C504629}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -8650,29 +10109,29 @@
       <c r="B1" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D1" s="36" t="s">
+      <c r="D1" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="37"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="37"/>
-      <c r="I1" s="38"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="33"/>
+      <c r="I1" s="34"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="36" t="s">
+      <c r="K1" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
-      <c r="N1" s="37"/>
-      <c r="O1" s="37"/>
-      <c r="P1" s="37"/>
-      <c r="Q1" s="38"/>
-      <c r="X1" s="36"/>
-      <c r="Y1" s="37"/>
-      <c r="Z1" s="38"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
+      <c r="Q1" s="34"/>
+      <c r="X1" s="32"/>
+      <c r="Y1" s="33"/>
+      <c r="Z1" s="34"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -8749,7 +10208,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="2">
-        <v>11.55</v>
+        <v>5.78</v>
       </c>
       <c r="H3" s="3">
         <v>0</v>
@@ -8760,11 +10219,11 @@
       <c r="J3" s="13"/>
       <c r="K3" s="3">
         <f>G53</f>
-        <v>226.42</v>
+        <v>113.21000000000001</v>
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>10.1</v>
+        <v>5.05</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
@@ -8772,7 +10231,7 @@
       </c>
       <c r="N3" s="7">
         <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
-        <v>0.10508826375007632</v>
+        <v>0.10510179400444034</v>
       </c>
       <c r="O3" s="6">
         <f>IF(B16=K3,MAX(E:E),"")</f>
@@ -8793,7 +10252,7 @@
       </c>
       <c r="Y3" s="3">
         <f>B16*-1</f>
-        <v>-226.42</v>
+        <v>-113.21</v>
       </c>
       <c r="Z3" s="2" t="str">
         <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
@@ -8818,7 +10277,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="2">
-        <v>11.55</v>
+        <v>5.78</v>
       </c>
       <c r="H4" s="3">
         <v>0</v>
@@ -8833,7 +10292,7 @@
       </c>
       <c r="Y4" s="3">
         <f>G3+H3-I3</f>
-        <v>11.55</v>
+        <v>5.78</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
@@ -8850,7 +10309,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="2">
-        <v>11.55</v>
+        <v>5.78</v>
       </c>
       <c r="H5" s="3">
         <v>0</v>
@@ -8865,7 +10324,7 @@
       </c>
       <c r="Y5" s="3">
         <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
-        <v>11.55</v>
+        <v>5.78</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
@@ -8882,7 +10341,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="2">
-        <v>11.55</v>
+        <v>5.78</v>
       </c>
       <c r="H6" s="3">
         <v>0</v>
@@ -8897,7 +10356,7 @@
       </c>
       <c r="Y6" s="3">
         <f t="shared" si="2"/>
-        <v>11.55</v>
+        <v>5.78</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
@@ -8914,7 +10373,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="2">
-        <v>11.55</v>
+        <v>5.78</v>
       </c>
       <c r="H7" s="3">
         <v>0</v>
@@ -8929,7 +10388,7 @@
       </c>
       <c r="Y7" s="3">
         <f t="shared" si="2"/>
-        <v>11.55</v>
+        <v>5.78</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
@@ -8951,10 +10410,10 @@
         <v>0</v>
       </c>
       <c r="G8" s="3">
-        <v>168.67</v>
+        <v>84.31</v>
       </c>
       <c r="H8" s="3">
-        <v>10.1</v>
+        <v>5.05</v>
       </c>
       <c r="I8" s="3">
         <v>0</v>
@@ -8966,7 +10425,7 @@
       </c>
       <c r="Y8" s="3">
         <f t="shared" si="2"/>
-        <v>11.55</v>
+        <v>5.78</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
@@ -8989,7 +10448,7 @@
       </c>
       <c r="Y9" s="3">
         <f t="shared" si="2"/>
-        <v>178.76999999999998</v>
+        <v>89.36</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
@@ -9142,7 +10601,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="3">
-        <v>226.42</v>
+        <v>113.21</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="6"/>
@@ -9898,11 +11357,11 @@
       <c r="F53" s="3"/>
       <c r="G53" s="3">
         <f>SUM(G3:G52)</f>
-        <v>226.42</v>
+        <v>113.21000000000001</v>
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>10.1</v>
+        <v>5.05</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
@@ -9940,7 +11399,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BE44972-B3BE-4780-9CE5-89011043CB83}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -9970,29 +11429,29 @@
       <c r="B1" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="36" t="s">
+      <c r="D1" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="37"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="37"/>
-      <c r="I1" s="38"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="33"/>
+      <c r="I1" s="34"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="36" t="s">
+      <c r="K1" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
-      <c r="N1" s="37"/>
-      <c r="O1" s="37"/>
-      <c r="P1" s="37"/>
-      <c r="Q1" s="38"/>
-      <c r="X1" s="36"/>
-      <c r="Y1" s="37"/>
-      <c r="Z1" s="38"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
+      <c r="Q1" s="34"/>
+      <c r="X1" s="32"/>
+      <c r="Y1" s="33"/>
+      <c r="Z1" s="34"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -10069,7 +11528,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="2">
-        <v>12.14</v>
+        <v>6.07</v>
       </c>
       <c r="H3" s="3">
         <v>0</v>
@@ -10080,11 +11539,11 @@
       <c r="J3" s="13"/>
       <c r="K3" s="3">
         <f>G53</f>
-        <v>222.28000000000003</v>
+        <v>111.14000000000001</v>
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>10.15</v>
+        <v>5.07</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
@@ -10092,7 +11551,7 @@
       </c>
       <c r="N3" s="7">
         <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
-        <v>0.10912081599235535</v>
+        <v>0.10901066660881042</v>
       </c>
       <c r="O3" s="6">
         <f>IF(B16=K3,MAX(E:E),"")</f>
@@ -10113,7 +11572,7 @@
       </c>
       <c r="Y3" s="3">
         <f>B16*-1</f>
-        <v>-222.28</v>
+        <v>-111.14</v>
       </c>
       <c r="Z3" s="2" t="str">
         <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
@@ -10138,7 +11597,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="2">
-        <v>12.14</v>
+        <v>6.07</v>
       </c>
       <c r="H4" s="3">
         <v>0</v>
@@ -10153,7 +11612,7 @@
       </c>
       <c r="Y4" s="3">
         <f>G3+H3-I3</f>
-        <v>12.14</v>
+        <v>6.07</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
@@ -10170,7 +11629,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="2">
-        <v>12.14</v>
+        <v>6.07</v>
       </c>
       <c r="H5" s="3">
         <v>0</v>
@@ -10185,7 +11644,7 @@
       </c>
       <c r="Y5" s="3">
         <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
-        <v>12.14</v>
+        <v>6.07</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
@@ -10202,7 +11661,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="2">
-        <v>12.14</v>
+        <v>6.07</v>
       </c>
       <c r="H6" s="3">
         <v>0</v>
@@ -10217,7 +11676,7 @@
       </c>
       <c r="Y6" s="3">
         <f t="shared" si="2"/>
-        <v>12.14</v>
+        <v>6.07</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
@@ -10234,7 +11693,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="2">
-        <v>12.14</v>
+        <v>6.07</v>
       </c>
       <c r="H7" s="3">
         <v>0</v>
@@ -10249,7 +11708,7 @@
       </c>
       <c r="Y7" s="3">
         <f t="shared" si="2"/>
-        <v>12.14</v>
+        <v>6.07</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
@@ -10271,10 +11730,10 @@
         <v>0</v>
       </c>
       <c r="G8" s="2">
-        <v>161.58000000000001</v>
+        <v>80.790000000000006</v>
       </c>
       <c r="H8" s="3">
-        <v>10.15</v>
+        <v>5.07</v>
       </c>
       <c r="I8" s="3">
         <v>0</v>
@@ -10286,7 +11745,7 @@
       </c>
       <c r="Y8" s="3">
         <f t="shared" si="2"/>
-        <v>12.14</v>
+        <v>6.07</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
@@ -10309,7 +11768,7 @@
       </c>
       <c r="Y9" s="3">
         <f t="shared" si="2"/>
-        <v>171.73000000000002</v>
+        <v>85.860000000000014</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
@@ -10462,7 +11921,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="3">
-        <v>222.28</v>
+        <v>111.14</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="6"/>
@@ -11218,11 +12677,11 @@
       <c r="F53" s="3"/>
       <c r="G53" s="3">
         <f>SUM(G3:G52)</f>
-        <v>222.28000000000003</v>
+        <v>111.14000000000001</v>
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>10.15</v>
+        <v>5.07</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
@@ -11260,7 +12719,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -11290,29 +12749,29 @@
       <c r="B1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="36" t="s">
+      <c r="D1" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="37"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="37"/>
-      <c r="I1" s="38"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="33"/>
+      <c r="I1" s="34"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="36" t="s">
+      <c r="K1" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
-      <c r="N1" s="37"/>
-      <c r="O1" s="37"/>
-      <c r="P1" s="37"/>
-      <c r="Q1" s="38"/>
-      <c r="X1" s="36"/>
-      <c r="Y1" s="37"/>
-      <c r="Z1" s="38"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
+      <c r="Q1" s="34"/>
+      <c r="X1" s="32"/>
+      <c r="Y1" s="33"/>
+      <c r="Z1" s="34"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -11389,7 +12848,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="3">
-        <v>12.28</v>
+        <v>6.14</v>
       </c>
       <c r="H3" s="3">
         <v>0</v>
@@ -11400,11 +12859,11 @@
       <c r="J3" s="13"/>
       <c r="K3" s="3">
         <f>G53</f>
-        <v>220</v>
+        <v>110</v>
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>10.32</v>
+        <v>5.16</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
@@ -11433,7 +12892,7 @@
       </c>
       <c r="Y3" s="3">
         <f>B16*-1</f>
-        <v>-220</v>
+        <v>-110</v>
       </c>
       <c r="Z3" s="2" t="str">
         <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
@@ -11458,7 +12917,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="3">
-        <v>12.28</v>
+        <v>6.14</v>
       </c>
       <c r="H4" s="3">
         <v>0</v>
@@ -11473,7 +12932,7 @@
       </c>
       <c r="Y4" s="3">
         <f>G3+H3-I3</f>
-        <v>12.28</v>
+        <v>6.14</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
@@ -11490,7 +12949,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="2">
-        <v>12.28</v>
+        <v>6.14</v>
       </c>
       <c r="H5" s="3">
         <v>0</v>
@@ -11505,7 +12964,7 @@
       </c>
       <c r="Y5" s="3">
         <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
-        <v>12.28</v>
+        <v>6.14</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
@@ -11522,7 +12981,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="3">
-        <v>12.28</v>
+        <v>6.14</v>
       </c>
       <c r="H6" s="3">
         <v>0</v>
@@ -11537,7 +12996,7 @@
       </c>
       <c r="Y6" s="3">
         <f t="shared" si="2"/>
-        <v>12.28</v>
+        <v>6.14</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
@@ -11554,7 +13013,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="3">
-        <v>12.28</v>
+        <v>6.14</v>
       </c>
       <c r="H7" s="3">
         <v>0</v>
@@ -11569,7 +13028,7 @@
       </c>
       <c r="Y7" s="3">
         <f t="shared" si="2"/>
-        <v>12.28</v>
+        <v>6.14</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
@@ -11591,10 +13050,10 @@
         <v>0</v>
       </c>
       <c r="G8" s="3">
-        <v>158.6</v>
+        <v>79.3</v>
       </c>
       <c r="H8" s="2">
-        <v>10.32</v>
+        <v>5.16</v>
       </c>
       <c r="I8" s="3">
         <v>0</v>
@@ -11606,7 +13065,7 @@
       </c>
       <c r="Y8" s="3">
         <f t="shared" si="2"/>
-        <v>12.28</v>
+        <v>6.14</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
@@ -11629,7 +13088,7 @@
       </c>
       <c r="Y9" s="3">
         <f t="shared" si="2"/>
-        <v>168.92</v>
+        <v>84.46</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
@@ -11782,7 +13241,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="3">
-        <v>220</v>
+        <v>110</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="6"/>
@@ -12538,11 +13997,11 @@
       <c r="F53" s="3"/>
       <c r="G53" s="3">
         <f>SUM(G3:G52)</f>
-        <v>220</v>
+        <v>110</v>
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>10.32</v>
+        <v>5.16</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
@@ -12624,7 +14083,7 @@
         <v>45881</v>
       </c>
       <c r="B2" s="3">
-        <v>205</v>
+        <v>102.5</v>
       </c>
       <c r="C2" s="3">
         <v>0</v>
@@ -12634,7 +14093,7 @@
       </c>
       <c r="F2" s="3">
         <f>SUM(B2:B35)</f>
-        <v>610</v>
+        <v>305</v>
       </c>
       <c r="G2" s="3">
         <f>SUM(C2:C35)</f>
@@ -12642,17 +14101,17 @@
       </c>
       <c r="H2" s="3">
         <f>SUM(D2:D35)</f>
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="I2" s="3">
         <f>F2-G2</f>
-        <v>610</v>
+        <v>305</v>
       </c>
       <c r="K2" s="3">
         <f>B2*-1</f>
-        <v>-205</v>
-      </c>
-      <c r="O2" s="33"/>
+        <v>-102.5</v>
+      </c>
+      <c r="O2" s="31"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
@@ -12665,7 +14124,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K3" s="3">
         <f t="shared" ref="K3:K9" si="0">B3*-1</f>
@@ -12677,7 +14136,7 @@
         <v>45882</v>
       </c>
       <c r="B4" s="3">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="C4" s="3">
         <v>0</v>
@@ -12687,7 +14146,7 @@
       </c>
       <c r="K4" s="3">
         <f t="shared" si="0"/>
-        <v>-5</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
@@ -12701,7 +14160,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K5" s="3">
         <f t="shared" si="0"/>
@@ -12713,7 +14172,7 @@
         <v>45898</v>
       </c>
       <c r="B6" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="C6" s="3">
         <v>0</v>
@@ -12723,7 +14182,7 @@
       </c>
       <c r="K6" s="3">
         <f t="shared" si="0"/>
-        <v>-200</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
@@ -12737,7 +14196,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K7" s="3">
         <f t="shared" si="0"/>
@@ -12749,7 +14208,7 @@
         <v>45929</v>
       </c>
       <c r="B8" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="C8" s="3">
         <v>0</v>
@@ -12759,7 +14218,7 @@
       </c>
       <c r="K8" s="3">
         <f t="shared" si="0"/>
-        <v>-200</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
@@ -12773,7 +14232,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K9" s="3">
         <f t="shared" si="0"/>
@@ -14113,14 +15572,14 @@
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="6">
         <f ca="1">TODAY()</f>
-        <v>46295</v>
+        <v>46307</v>
       </c>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
       <c r="D200" s="1"/>
       <c r="K200" s="25">
         <f>Overview!W3</f>
-        <v>687.59</v>
+        <v>348.4</v>
       </c>
     </row>
   </sheetData>
@@ -14129,6 +15588,1290 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFBE6089-EA35-40E4-A336-23F088184108}">
+  <dimension ref="A1:Z53"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="40.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="9" width="10.7109375" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" customWidth="1"/>
+    <col min="11" max="14" width="10.7109375" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" customWidth="1"/>
+    <col min="16" max="17" width="10.7109375" customWidth="1"/>
+    <col min="18" max="23" width="8.7109375" customWidth="1"/>
+    <col min="24" max="24" width="12.7109375" style="13" customWidth="1"/>
+    <col min="25" max="25" width="10.7109375" style="13" customWidth="1"/>
+    <col min="26" max="26" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="33"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="33"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
+      <c r="Q1" s="34"/>
+      <c r="X1" s="32"/>
+      <c r="Y1" s="33"/>
+      <c r="Z1" s="34"/>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="9"/>
+      <c r="K2" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O2" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="P2" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q2" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="X2" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y2" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z2" s="11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" s="6">
+        <v>46331</v>
+      </c>
+      <c r="E3" s="6"/>
+      <c r="F3" s="18" t="str">
+        <f t="shared" ref="F3:F52" si="0">IF(E3&gt;0,E3-D3,"")</f>
+        <v/>
+      </c>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="3">
+        <f>G53</f>
+        <v>0</v>
+      </c>
+      <c r="L3" s="3">
+        <f>H53</f>
+        <v>0</v>
+      </c>
+      <c r="M3" s="3">
+        <f>I53</f>
+        <v>0</v>
+      </c>
+      <c r="N3" s="7" t="str">
+        <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
+        <v/>
+      </c>
+      <c r="O3" s="6" t="str">
+        <f>IF(B16=K3,MAX(E:E),"")</f>
+        <v/>
+      </c>
+      <c r="P3" s="2" t="str">
+        <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
+        <v/>
+      </c>
+      <c r="Q3" s="2" t="str">
+        <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
+        <v/>
+      </c>
+      <c r="T3" s="15"/>
+      <c r="X3" s="6">
+        <f>B9</f>
+        <v>46300</v>
+      </c>
+      <c r="Y3" s="3">
+        <f>B16*-1</f>
+        <v>-96.08</v>
+      </c>
+      <c r="Z3" s="2" t="str">
+        <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="6">
+        <v>46363</v>
+      </c>
+      <c r="E4" s="6"/>
+      <c r="F4" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="9"/>
+      <c r="X4" s="6">
+        <f>E3</f>
+        <v>0</v>
+      </c>
+      <c r="Y4" s="3">
+        <f>G3+H3-I3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A5" s="5"/>
+      <c r="B5" s="6"/>
+      <c r="D5" s="6">
+        <v>46392</v>
+      </c>
+      <c r="E5" s="6"/>
+      <c r="F5" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="9"/>
+      <c r="X5" s="6">
+        <f t="shared" ref="X5:X52" si="1">E4</f>
+        <v>0</v>
+      </c>
+      <c r="Y5" s="3">
+        <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A6" s="5"/>
+      <c r="B6" s="6"/>
+      <c r="D6" s="6">
+        <v>46423</v>
+      </c>
+      <c r="E6" s="6"/>
+      <c r="F6" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="9"/>
+      <c r="X6" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A7" s="5"/>
+      <c r="B7" s="6"/>
+      <c r="D7" s="6">
+        <v>46451</v>
+      </c>
+      <c r="E7" s="6"/>
+      <c r="F7" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="13"/>
+      <c r="X7" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="6" t="str">
+        <f>DATEDIF(B9,B11,"y") &amp; " m. " &amp; DATEDIF(B9,B11,"ym") &amp; " mėn. " &amp; DATEDIF(B9,B11,"md") &amp; " d."</f>
+        <v>0 m. 6 mėn. 0 d.</v>
+      </c>
+      <c r="D8" s="6">
+        <v>46482</v>
+      </c>
+      <c r="E8" s="6"/>
+      <c r="F8" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G8" s="2"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="9"/>
+      <c r="X8" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="6">
+        <v>46300</v>
+      </c>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G9" s="2"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="13"/>
+      <c r="X9" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="6">
+        <v>46313</v>
+      </c>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="13"/>
+      <c r="X10" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y10" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <v>46482</v>
+      </c>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G11" s="3"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="13"/>
+      <c r="X11" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y11" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="18">
+        <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
+        <v>175</v>
+      </c>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G12" s="3"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="13"/>
+      <c r="X12" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y12" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A13" s="5"/>
+      <c r="B13" s="3"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="13"/>
+      <c r="N13" s="15"/>
+      <c r="X13" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="19"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="13"/>
+      <c r="X14" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="10"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="17"/>
+      <c r="M15" s="17"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="17"/>
+      <c r="X15" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="3">
+        <v>96.08</v>
+      </c>
+      <c r="D16" s="10"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="21"/>
+      <c r="P16" s="13"/>
+      <c r="Q16" s="13"/>
+      <c r="X16" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y16" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D17" s="10"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="13"/>
+      <c r="X17" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y17" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D18" s="10"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="13"/>
+      <c r="X18" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y18" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D19" s="10"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="13"/>
+      <c r="X19" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y19" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D20" s="10"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="13"/>
+      <c r="X20" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D21" s="10"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="13"/>
+      <c r="X21" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y21" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D22" s="10"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="13"/>
+      <c r="X22" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D23" s="10"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="13"/>
+      <c r="X23" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y23" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D24" s="10"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="13"/>
+      <c r="X24" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D25" s="10"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="13"/>
+      <c r="X25" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D26" s="10"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="13"/>
+      <c r="X26" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y26" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D27" s="10"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="13"/>
+      <c r="X27" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y27" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D28" s="10"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="13"/>
+      <c r="X28" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D29" s="10"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="13"/>
+      <c r="X29" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D30" s="10"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="13"/>
+      <c r="X30" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D31" s="10"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="13"/>
+      <c r="X31" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D32" s="10"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="13"/>
+      <c r="X32" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D33" s="10"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="13"/>
+      <c r="X33" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y33" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D34" s="10"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="13"/>
+      <c r="X34" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D35" s="10"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="13"/>
+      <c r="X35" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y35" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D36" s="10"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="13"/>
+      <c r="X36" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y36" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D37" s="10"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="13"/>
+      <c r="X37" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y37" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D38" s="10"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="13"/>
+      <c r="X38" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y38" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D39" s="10"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="13"/>
+      <c r="X39" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y39" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D40" s="10"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="13"/>
+      <c r="X40" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y40" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D41" s="10"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="13"/>
+      <c r="X41" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y41" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D42" s="10"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="13"/>
+      <c r="X42" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D43" s="10"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="13"/>
+      <c r="X43" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y43" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D44" s="10"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="13"/>
+      <c r="X44" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y44" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D45" s="10"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="13"/>
+      <c r="X45" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y45" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D46" s="10"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="13"/>
+      <c r="X46" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y46" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D47" s="10"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="13"/>
+      <c r="X47" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D48" s="10"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="13"/>
+      <c r="X48" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y48" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D49" s="10"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="13"/>
+      <c r="X49" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y49" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D50" s="10"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="13"/>
+      <c r="X50" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D51" s="10"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="13"/>
+      <c r="X51" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D52" s="10"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="9"/>
+      <c r="X52" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y52" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D53" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E53" s="14"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3">
+        <f>SUM(G3:G52)</f>
+        <v>0</v>
+      </c>
+      <c r="H53" s="3">
+        <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
+        <v>0</v>
+      </c>
+      <c r="I53" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="X1:Z1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="expression" dxfId="59" priority="1">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="58" priority="2">
+      <formula>$B$16=$K$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P3">
+    <cfRule type="expression" dxfId="57" priority="3">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z3">
+    <cfRule type="expression" dxfId="56" priority="4">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB14D149-944D-412E-95CC-4C7E13B9E24E}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -14155,29 +16898,29 @@
       <c r="B1" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D1" s="36" t="s">
+      <c r="D1" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="37"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="37"/>
-      <c r="I1" s="38"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="33"/>
+      <c r="I1" s="34"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="36" t="s">
+      <c r="K1" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
-      <c r="N1" s="37"/>
-      <c r="O1" s="37"/>
-      <c r="P1" s="37"/>
-      <c r="Q1" s="38"/>
-      <c r="X1" s="36"/>
-      <c r="Y1" s="37"/>
-      <c r="Z1" s="38"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
+      <c r="Q1" s="34"/>
+      <c r="X1" s="32"/>
+      <c r="Y1" s="33"/>
+      <c r="Z1" s="34"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -14186,53 +16929,53 @@
       <c r="B2" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D2" s="35" t="s">
+      <c r="D2" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="35" t="s">
+      <c r="E2" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="34" t="s">
+      <c r="F2" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="G2" s="35" t="s">
+      <c r="G2" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="35" t="s">
+      <c r="H2" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="35" t="s">
+      <c r="I2" s="11" t="s">
         <v>18</v>
       </c>
       <c r="J2" s="9"/>
-      <c r="K2" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="L2" s="35" t="s">
+      <c r="K2" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="M2" s="35" t="s">
+      <c r="M2" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="35" t="s">
+      <c r="N2" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="O2" s="35" t="s">
+      <c r="O2" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="P2" s="35" t="s">
+      <c r="P2" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="Q2" s="35" t="s">
+      <c r="Q2" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="X2" s="35" t="s">
+      <c r="X2" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="Y2" s="35" t="s">
+      <c r="Y2" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="Z2" s="35" t="s">
+      <c r="Z2" s="11" t="s">
         <v>30</v>
       </c>
     </row>
@@ -14246,18 +16989,26 @@
       <c r="D3" s="6">
         <v>46300</v>
       </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="18" t="str">
+      <c r="E3" s="6">
+        <v>46300</v>
+      </c>
+      <c r="F3" s="18">
         <f t="shared" ref="F3:F52" si="0">IF(E3&gt;0,E3-D3,"")</f>
-        <v/>
-      </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>3.26</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0</v>
+      </c>
       <c r="J3" s="13"/>
       <c r="K3" s="3">
         <f>G53</f>
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="L3" s="3">
         <f>H53</f>
@@ -14290,7 +17041,7 @@
       </c>
       <c r="Y3" s="3">
         <f>B16*-1</f>
-        <v>-197.5</v>
+        <v>-98.75</v>
       </c>
       <c r="Z3" s="2" t="str">
         <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
@@ -14318,18 +17069,18 @@
       <c r="J4" s="9"/>
       <c r="X4" s="6">
         <f>E3</f>
-        <v>0</v>
+        <v>46300</v>
       </c>
       <c r="Y4" s="3">
         <f>G3+H3-I3</f>
-        <v>0</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
       <c r="B5" s="6"/>
       <c r="D5" s="6">
-        <v>46361</v>
+        <v>46363</v>
       </c>
       <c r="E5" s="6"/>
       <c r="F5" s="18" t="str">
@@ -14510,7 +17261,7 @@
       </c>
       <c r="B12" s="18">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -14614,7 +17365,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="3">
-        <v>197.5</v>
+        <v>98.75</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="6"/>
@@ -15370,7 +18121,7 @@
       <c r="F53" s="3"/>
       <c r="G53" s="3">
         <f>SUM(G3:G52)</f>
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
@@ -15412,7 +18163,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40E5D5DD-CBD2-4FD8-9F41-16B9523FDC2D}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -15439,29 +18190,29 @@
       <c r="B1" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="D1" s="36" t="s">
+      <c r="D1" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="37"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="37"/>
-      <c r="I1" s="38"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="33"/>
+      <c r="I1" s="34"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="36" t="s">
+      <c r="K1" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
-      <c r="N1" s="37"/>
-      <c r="O1" s="37"/>
-      <c r="P1" s="37"/>
-      <c r="Q1" s="38"/>
-      <c r="X1" s="36"/>
-      <c r="Y1" s="37"/>
-      <c r="Z1" s="38"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
+      <c r="Q1" s="34"/>
+      <c r="X1" s="32"/>
+      <c r="Y1" s="33"/>
+      <c r="Z1" s="34"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -15470,53 +18221,53 @@
       <c r="B2" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D2" s="32" t="s">
+      <c r="D2" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="32" t="s">
+      <c r="E2" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="31" t="s">
+      <c r="F2" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="G2" s="32" t="s">
+      <c r="G2" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="32" t="s">
+      <c r="H2" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="32" t="s">
+      <c r="I2" s="11" t="s">
         <v>18</v>
       </c>
       <c r="J2" s="9"/>
-      <c r="K2" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="L2" s="32" t="s">
+      <c r="K2" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="M2" s="32" t="s">
+      <c r="M2" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="32" t="s">
+      <c r="N2" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="O2" s="32" t="s">
+      <c r="O2" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="P2" s="32" t="s">
+      <c r="P2" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="Q2" s="32" t="s">
+      <c r="Q2" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="X2" s="32" t="s">
+      <c r="X2" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="Y2" s="32" t="s">
+      <c r="Y2" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="Z2" s="32" t="s">
+      <c r="Z2" s="11" t="s">
         <v>30</v>
       </c>
     </row>
@@ -15538,7 +18289,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="3">
-        <v>13.02</v>
+        <v>6.51</v>
       </c>
       <c r="H3" s="3">
         <v>0</v>
@@ -15582,7 +18333,7 @@
       </c>
       <c r="Y3" s="3">
         <f>B16*-1</f>
-        <v>-185.68</v>
+        <v>-92.84</v>
       </c>
       <c r="Z3" s="2" t="str">
         <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
@@ -15599,14 +18350,22 @@
       <c r="D4" s="6">
         <v>46300</v>
       </c>
-      <c r="E4" s="6"/>
-      <c r="F4" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="E4" s="6">
+        <v>46300</v>
+      </c>
+      <c r="F4" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>6.51</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3">
+        <v>0</v>
+      </c>
       <c r="J4" s="9"/>
       <c r="X4" s="6">
         <f>E3</f>
@@ -15614,7 +18373,7 @@
       </c>
       <c r="Y4" s="3">
         <f>G3+H3-I3</f>
-        <v>13.02</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
@@ -15634,18 +18393,18 @@
       <c r="J5" s="9"/>
       <c r="X5" s="6">
         <f t="shared" ref="X5:X52" si="1">E4</f>
-        <v>0</v>
+        <v>46300</v>
       </c>
       <c r="Y5" s="3">
         <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
-        <v>0</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="B6" s="6"/>
       <c r="D6" s="6">
-        <v>46361</v>
+        <v>46363</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="18" t="str">
@@ -15802,7 +18561,7 @@
       </c>
       <c r="B12" s="18">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -15906,7 +18665,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="3">
-        <v>185.68</v>
+        <v>92.84</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="6"/>
@@ -16704,7 +19463,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EA74071-CEE0-4172-8957-6D5916CFD11C}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -16731,29 +19490,29 @@
       <c r="B1" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="36" t="s">
+      <c r="D1" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="37"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="37"/>
-      <c r="I1" s="38"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="33"/>
+      <c r="I1" s="34"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="36" t="s">
+      <c r="K1" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
-      <c r="N1" s="37"/>
-      <c r="O1" s="37"/>
-      <c r="P1" s="37"/>
-      <c r="Q1" s="38"/>
-      <c r="X1" s="36"/>
-      <c r="Y1" s="37"/>
-      <c r="Z1" s="38"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
+      <c r="Q1" s="34"/>
+      <c r="X1" s="32"/>
+      <c r="Y1" s="33"/>
+      <c r="Z1" s="34"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -16830,7 +19589,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="3">
-        <v>1.72</v>
+        <v>0.86</v>
       </c>
       <c r="H3" s="3">
         <v>0</v>
@@ -16841,7 +19600,7 @@
       <c r="J3" s="13"/>
       <c r="K3" s="3">
         <f>G53</f>
-        <v>3.44</v>
+        <v>2.58</v>
       </c>
       <c r="L3" s="3">
         <f>H53</f>
@@ -16874,7 +19633,7 @@
       </c>
       <c r="Y3" s="3">
         <f>B16*-1</f>
-        <v>-71.86</v>
+        <v>-35.93</v>
       </c>
       <c r="Z3" s="2" t="str">
         <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
@@ -16899,7 +19658,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="3">
-        <v>1.72</v>
+        <v>0.86</v>
       </c>
       <c r="H4" s="3">
         <v>0</v>
@@ -16914,7 +19673,7 @@
       </c>
       <c r="Y4" s="3">
         <f>G3+H3-I3</f>
-        <v>1.72</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
@@ -16923,14 +19682,22 @@
       <c r="D5" s="6">
         <v>46300</v>
       </c>
-      <c r="E5" s="6"/>
-      <c r="F5" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
+      <c r="E5" s="6">
+        <v>46300</v>
+      </c>
+      <c r="F5" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0.86</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3">
+        <v>0</v>
+      </c>
       <c r="J5" s="9"/>
       <c r="X5" s="6">
         <f t="shared" ref="X5:X52" si="1">E4</f>
@@ -16938,7 +19705,7 @@
       </c>
       <c r="Y5" s="3">
         <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
-        <v>1.72</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
@@ -16958,18 +19725,18 @@
       <c r="J6" s="9"/>
       <c r="X6" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46300</v>
       </c>
       <c r="Y6" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
       <c r="B7" s="6"/>
       <c r="D7" s="6">
-        <v>46361</v>
+        <v>46363</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="18" t="str">
@@ -16977,8 +19744,8 @@
         <v/>
       </c>
       <c r="G7" s="3"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
       <c r="J7" s="13"/>
       <c r="X7" s="6">
         <f t="shared" si="1"/>
@@ -17102,7 +19869,7 @@
       </c>
       <c r="B12" s="18">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -17206,7 +19973,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="3">
-        <v>71.86</v>
+        <v>35.93</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="6"/>
@@ -17962,7 +20729,7 @@
       <c r="F53" s="3"/>
       <c r="G53" s="3">
         <f>SUM(G3:G52)</f>
-        <v>3.44</v>
+        <v>2.58</v>
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
@@ -18004,7 +20771,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E39A4C94-8C03-41D4-B944-5DB24FED2BD0}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -18031,29 +20798,29 @@
       <c r="B1" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D1" s="36" t="s">
+      <c r="D1" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="37"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="37"/>
-      <c r="I1" s="38"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="33"/>
+      <c r="I1" s="34"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="36" t="s">
+      <c r="K1" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
-      <c r="N1" s="37"/>
-      <c r="O1" s="37"/>
-      <c r="P1" s="37"/>
-      <c r="Q1" s="38"/>
-      <c r="X1" s="36"/>
-      <c r="Y1" s="37"/>
-      <c r="Z1" s="38"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
+      <c r="Q1" s="34"/>
+      <c r="X1" s="32"/>
+      <c r="Y1" s="33"/>
+      <c r="Z1" s="34"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -18130,7 +20897,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="3">
-        <v>4.1399999999999997</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="H3" s="3">
         <v>0</v>
@@ -18141,7 +20908,7 @@
       <c r="J3" s="13"/>
       <c r="K3" s="3">
         <f>G53</f>
-        <v>12.419999999999998</v>
+        <v>8.2799999999999994</v>
       </c>
       <c r="L3" s="3">
         <f>H53</f>
@@ -18174,7 +20941,7 @@
       </c>
       <c r="Y3" s="3">
         <f>B16*-1</f>
-        <v>-69.010000000000005</v>
+        <v>-34.5</v>
       </c>
       <c r="Z3" s="2" t="str">
         <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
@@ -18198,7 +20965,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="3">
-        <v>4.1399999999999997</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="H4" s="3">
         <v>0</v>
@@ -18213,7 +20980,7 @@
       </c>
       <c r="Y4" s="3">
         <f>G3+H3-I3</f>
-        <v>4.1399999999999997</v>
+        <v>2.0699999999999998</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
@@ -18230,7 +20997,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="3">
-        <v>4.1399999999999997</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="H5" s="3">
         <v>0</v>
@@ -18245,7 +21012,7 @@
       </c>
       <c r="Y5" s="3">
         <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
-        <v>4.1399999999999997</v>
+        <v>2.0699999999999998</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
@@ -18254,14 +21021,22 @@
       <c r="D6" s="6">
         <v>46300</v>
       </c>
-      <c r="E6" s="6"/>
-      <c r="F6" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
+      <c r="E6" s="6">
+        <v>46300</v>
+      </c>
+      <c r="F6" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="2">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3">
+        <v>0</v>
+      </c>
       <c r="J6" s="9"/>
       <c r="X6" s="6">
         <f t="shared" si="1"/>
@@ -18269,7 +21044,7 @@
       </c>
       <c r="Y6" s="3">
         <f t="shared" si="2"/>
-        <v>4.1399999999999997</v>
+        <v>2.0699999999999998</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
@@ -18289,11 +21064,11 @@
       <c r="J7" s="13"/>
       <c r="X7" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46300</v>
       </c>
       <c r="Y7" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2.0699999999999998</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
@@ -18409,7 +21184,7 @@
       </c>
       <c r="B12" s="18">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -18513,7 +21288,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="3">
-        <v>69.010000000000005</v>
+        <v>34.5</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="6"/>
@@ -19269,7 +22044,7 @@
       <c r="F53" s="3"/>
       <c r="G53" s="3">
         <f>SUM(G3:G52)</f>
-        <v>12.419999999999998</v>
+        <v>8.2799999999999994</v>
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
@@ -19311,7 +22086,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51596B63-3E30-4F0D-ACA7-3B11B25E71A9}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -19338,29 +22113,29 @@
       <c r="B1" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="36" t="s">
+      <c r="D1" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="37"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="37"/>
-      <c r="I1" s="38"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="33"/>
+      <c r="I1" s="34"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="36" t="s">
+      <c r="K1" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
-      <c r="N1" s="37"/>
-      <c r="O1" s="37"/>
-      <c r="P1" s="37"/>
-      <c r="Q1" s="38"/>
-      <c r="X1" s="36"/>
-      <c r="Y1" s="37"/>
-      <c r="Z1" s="38"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
+      <c r="Q1" s="34"/>
+      <c r="X1" s="32"/>
+      <c r="Y1" s="33"/>
+      <c r="Z1" s="34"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -19437,7 +22212,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="3">
-        <v>6.13</v>
+        <v>3.06</v>
       </c>
       <c r="H3" s="3">
         <v>0</v>
@@ -19448,7 +22223,7 @@
       <c r="J3" s="13"/>
       <c r="K3" s="3">
         <f>G53</f>
-        <v>24.52</v>
+        <v>15.3</v>
       </c>
       <c r="L3" s="3">
         <f>H53</f>
@@ -19481,7 +22256,7 @@
       </c>
       <c r="Y3" s="3">
         <f>B16*-1</f>
-        <v>-65.53</v>
+        <v>-32.770000000000003</v>
       </c>
       <c r="Z3" s="2" t="str">
         <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
@@ -19506,7 +22281,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="2">
-        <v>6.13</v>
+        <v>3.06</v>
       </c>
       <c r="H4" s="3">
         <v>0</v>
@@ -19521,7 +22296,7 @@
       </c>
       <c r="Y4" s="3">
         <f>G3+H3-I3</f>
-        <v>6.13</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
@@ -19538,7 +22313,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="3">
-        <v>6.13</v>
+        <v>3.06</v>
       </c>
       <c r="H5" s="3">
         <v>0</v>
@@ -19553,7 +22328,7 @@
       </c>
       <c r="Y5" s="3">
         <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
-        <v>6.13</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
@@ -19570,7 +22345,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="2">
-        <v>6.13</v>
+        <v>3.06</v>
       </c>
       <c r="H6" s="3">
         <v>0</v>
@@ -19585,7 +22360,7 @@
       </c>
       <c r="Y6" s="3">
         <f t="shared" si="2"/>
-        <v>6.13</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
@@ -19594,14 +22369,22 @@
       <c r="D7" s="6">
         <v>46300</v>
       </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
+      <c r="E7" s="6">
+        <v>46300</v>
+      </c>
+      <c r="F7" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>3.06</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3">
+        <v>0</v>
+      </c>
       <c r="J7" s="13"/>
       <c r="X7" s="6">
         <f t="shared" si="1"/>
@@ -19609,7 +22392,7 @@
       </c>
       <c r="Y7" s="3">
         <f t="shared" si="2"/>
-        <v>6.13</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
@@ -19634,11 +22417,11 @@
       <c r="J8" s="9"/>
       <c r="X8" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46300</v>
       </c>
       <c r="Y8" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
@@ -19725,7 +22508,7 @@
       </c>
       <c r="B12" s="18">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -19829,7 +22612,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="3">
-        <v>65.53</v>
+        <v>32.770000000000003</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="6"/>
@@ -20585,7 +23368,7 @@
       <c r="F53" s="3"/>
       <c r="G53" s="3">
         <f>SUM(G3:G52)</f>
-        <v>24.52</v>
+        <v>15.3</v>
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
@@ -20627,8 +23410,11 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6787A89-4537-4E64-91BF-0AA0F96019C3}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -20654,29 +23440,29 @@
       <c r="B1" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="D1" s="36" t="s">
+      <c r="D1" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="37"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="37"/>
-      <c r="I1" s="38"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="33"/>
+      <c r="I1" s="34"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="36" t="s">
+      <c r="K1" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
-      <c r="N1" s="37"/>
-      <c r="O1" s="37"/>
-      <c r="P1" s="37"/>
-      <c r="Q1" s="38"/>
-      <c r="X1" s="36"/>
-      <c r="Y1" s="37"/>
-      <c r="Z1" s="38"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
+      <c r="Q1" s="34"/>
+      <c r="X1" s="32"/>
+      <c r="Y1" s="33"/>
+      <c r="Z1" s="34"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -20753,7 +23539,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="3">
-        <v>10.8</v>
+        <v>5.4</v>
       </c>
       <c r="H3" s="3">
         <v>0</v>
@@ -20764,31 +23550,31 @@
       <c r="J3" s="13"/>
       <c r="K3" s="3">
         <f>G53</f>
-        <v>54</v>
+        <v>102.7</v>
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>0</v>
+        <v>4.6100000000000003</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
         <v>0</v>
       </c>
-      <c r="N3" s="7" t="str">
+      <c r="N3" s="7">
         <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
-        <v/>
-      </c>
-      <c r="O3" s="6" t="str">
+        <v>0.10618163943290709</v>
+      </c>
+      <c r="O3" s="6">
         <f>IF(B16=K3,MAX(E:E),"")</f>
-        <v/>
+        <v>46300</v>
       </c>
       <c r="P3" s="2" t="str">
         <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
         <v/>
       </c>
-      <c r="Q3" s="2" t="str">
+      <c r="Q3" s="2">
         <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T3" s="15"/>
       <c r="X3" s="6">
@@ -20797,7 +23583,7 @@
       </c>
       <c r="Y3" s="3">
         <f>B16*-1</f>
-        <v>-205.39</v>
+        <v>-102.7</v>
       </c>
       <c r="Z3" s="2" t="str">
         <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
@@ -20822,7 +23608,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="3">
-        <v>10.8</v>
+        <v>5.4</v>
       </c>
       <c r="H4" s="3">
         <v>0</v>
@@ -20837,7 +23623,7 @@
       </c>
       <c r="Y4" s="3">
         <f>G3+H3-I3</f>
-        <v>10.8</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
@@ -20854,7 +23640,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="3">
-        <v>10.8</v>
+        <v>5.4</v>
       </c>
       <c r="H5" s="3">
         <v>0</v>
@@ -20869,7 +23655,7 @@
       </c>
       <c r="Y5" s="3">
         <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
-        <v>10.8</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
@@ -20886,7 +23672,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="3">
-        <v>10.8</v>
+        <v>5.4</v>
       </c>
       <c r="H6" s="3">
         <v>0</v>
@@ -20901,7 +23687,7 @@
       </c>
       <c r="Y6" s="3">
         <f t="shared" si="2"/>
-        <v>10.8</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
@@ -20918,7 +23704,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="3">
-        <v>10.8</v>
+        <v>5.4</v>
       </c>
       <c r="H7" s="3">
         <v>0</v>
@@ -20933,7 +23719,7 @@
       </c>
       <c r="Y7" s="3">
         <f t="shared" si="2"/>
-        <v>10.8</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
@@ -20947,14 +23733,22 @@
       <c r="D8" s="6">
         <v>46300</v>
       </c>
-      <c r="E8" s="6"/>
-      <c r="F8" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
+      <c r="E8" s="6">
+        <v>46300</v>
+      </c>
+      <c r="F8" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <v>75.7</v>
+      </c>
+      <c r="H8" s="3">
+        <v>4.6100000000000003</v>
+      </c>
+      <c r="I8" s="3">
+        <v>0</v>
+      </c>
       <c r="J8" s="9"/>
       <c r="X8" s="6">
         <f t="shared" si="1"/>
@@ -20962,7 +23756,7 @@
       </c>
       <c r="Y8" s="3">
         <f t="shared" si="2"/>
-        <v>10.8</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
@@ -20984,11 +23778,11 @@
       <c r="J9" s="13"/>
       <c r="X9" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46300</v>
       </c>
       <c r="Y9" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>80.31</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
@@ -21047,9 +23841,9 @@
       <c r="A12" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B12" s="18">
+      <c r="B12" s="18" t="str">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>5</v>
+        <v/>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -21153,7 +23947,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="3">
-        <v>205.39</v>
+        <v>102.7</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="6"/>
@@ -21909,11 +24703,11 @@
       <c r="F53" s="3"/>
       <c r="G53" s="3">
         <f>SUM(G3:G52)</f>
-        <v>54</v>
+        <v>102.7</v>
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0</v>
+        <v>4.6100000000000003</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
@@ -21949,1339 +24743,4 @@
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29B83440-5743-4944-A92C-7C00476AA6BD}">
-  <sheetPr>
-    <tabColor rgb="FF92D050"/>
-  </sheetPr>
-  <dimension ref="A1:Z53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="25.7109375" customWidth="1"/>
-    <col min="2" max="2" width="40.7109375" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" customWidth="1"/>
-    <col min="4" max="5" width="12.7109375" customWidth="1"/>
-    <col min="6" max="9" width="10.7109375" customWidth="1"/>
-    <col min="10" max="10" width="8.7109375" customWidth="1"/>
-    <col min="11" max="14" width="10.7109375" customWidth="1"/>
-    <col min="15" max="15" width="12.7109375" customWidth="1"/>
-    <col min="16" max="17" width="10.7109375" customWidth="1"/>
-    <col min="18" max="23" width="8.7109375" customWidth="1"/>
-    <col min="24" max="24" width="12.7109375" style="13" customWidth="1"/>
-    <col min="25" max="25" width="10.7109375" style="13" customWidth="1"/>
-    <col min="26" max="26" width="10.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="D1" s="36" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="37"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="37"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
-      <c r="N1" s="37"/>
-      <c r="O1" s="37"/>
-      <c r="P1" s="37"/>
-      <c r="Q1" s="38"/>
-      <c r="X1" s="36"/>
-      <c r="Y1" s="37"/>
-      <c r="Z1" s="38"/>
-    </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="F2" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="G2" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="9"/>
-      <c r="K2" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="L2" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="M2" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="N2" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="O2" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="P2" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q2" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="X2" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y2" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z2" s="11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="D3" s="6">
-        <v>46118</v>
-      </c>
-      <c r="E3" s="6">
-        <v>46118</v>
-      </c>
-      <c r="F3" s="18">
-        <f t="shared" ref="F3:F52" si="0">IF(E3&gt;0,E3-D3,"")</f>
-        <v>0</v>
-      </c>
-      <c r="G3" s="3">
-        <v>9.6199999999999992</v>
-      </c>
-      <c r="H3" s="3">
-        <v>0</v>
-      </c>
-      <c r="I3" s="3">
-        <v>0</v>
-      </c>
-      <c r="J3" s="13"/>
-      <c r="K3" s="3">
-        <f>G53</f>
-        <v>200.38</v>
-      </c>
-      <c r="L3" s="3">
-        <f>H53</f>
-        <v>9.11</v>
-      </c>
-      <c r="M3" s="3">
-        <f>I53</f>
-        <v>0</v>
-      </c>
-      <c r="N3" s="7">
-        <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
-        <v>0.10385321974754333</v>
-      </c>
-      <c r="O3" s="6">
-        <f>IF(B16=K3,MAX(E:E),"")</f>
-        <v>46272</v>
-      </c>
-      <c r="P3" s="2" t="str">
-        <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
-        <v/>
-      </c>
-      <c r="Q3" s="2">
-        <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
-        <v>0</v>
-      </c>
-      <c r="T3" s="15"/>
-      <c r="X3" s="6">
-        <f>B9</f>
-        <v>46086</v>
-      </c>
-      <c r="Y3" s="3">
-        <f>B16*-1</f>
-        <v>-200.38</v>
-      </c>
-      <c r="Z3" s="2" t="str">
-        <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="D4" s="6">
-        <v>46147</v>
-      </c>
-      <c r="E4" s="6">
-        <v>46147</v>
-      </c>
-      <c r="F4" s="18">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G4" s="2">
-        <v>9.6199999999999992</v>
-      </c>
-      <c r="H4" s="3">
-        <v>0</v>
-      </c>
-      <c r="I4" s="3">
-        <v>0</v>
-      </c>
-      <c r="J4" s="9"/>
-      <c r="X4" s="6">
-        <f>E3</f>
-        <v>46118</v>
-      </c>
-      <c r="Y4" s="3">
-        <f>G3+H3-I3</f>
-        <v>9.6199999999999992</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A5" s="5"/>
-      <c r="B5" s="6"/>
-      <c r="D5" s="6">
-        <v>46178</v>
-      </c>
-      <c r="E5" s="6">
-        <v>46178</v>
-      </c>
-      <c r="F5" s="18">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G5" s="2">
-        <v>9.6199999999999992</v>
-      </c>
-      <c r="H5" s="3">
-        <v>0</v>
-      </c>
-      <c r="I5" s="3">
-        <v>0</v>
-      </c>
-      <c r="J5" s="9"/>
-      <c r="X5" s="6">
-        <f t="shared" ref="X5:X52" si="1">E4</f>
-        <v>46147</v>
-      </c>
-      <c r="Y5" s="3">
-        <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
-        <v>9.6199999999999992</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A6" s="5"/>
-      <c r="B6" s="6"/>
-      <c r="D6" s="6">
-        <v>46209</v>
-      </c>
-      <c r="E6" s="6">
-        <v>46209</v>
-      </c>
-      <c r="F6" s="18">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G6" s="2">
-        <v>9.6199999999999992</v>
-      </c>
-      <c r="H6" s="3">
-        <v>0</v>
-      </c>
-      <c r="I6" s="3">
-        <v>0</v>
-      </c>
-      <c r="J6" s="9"/>
-      <c r="X6" s="6">
-        <f t="shared" si="1"/>
-        <v>46178</v>
-      </c>
-      <c r="Y6" s="3">
-        <f t="shared" si="2"/>
-        <v>9.6199999999999992</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A7" s="5"/>
-      <c r="B7" s="6"/>
-      <c r="D7" s="6">
-        <v>46239</v>
-      </c>
-      <c r="E7" s="6">
-        <v>46239</v>
-      </c>
-      <c r="F7" s="18">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G7" s="3">
-        <v>9.32</v>
-      </c>
-      <c r="H7" s="3">
-        <v>0</v>
-      </c>
-      <c r="I7" s="3">
-        <v>0</v>
-      </c>
-      <c r="J7" s="13"/>
-      <c r="X7" s="6">
-        <f t="shared" si="1"/>
-        <v>46209</v>
-      </c>
-      <c r="Y7" s="3">
-        <f t="shared" si="2"/>
-        <v>9.6199999999999992</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="6" t="str">
-        <f>DATEDIF(B9,B11,"y") &amp; " m. " &amp; DATEDIF(B9,B11,"ym") &amp; " mėn. " &amp; DATEDIF(B9,B11,"md") &amp; " d."</f>
-        <v>0 m. 6 mėn. 2 d.</v>
-      </c>
-      <c r="D8" s="6">
-        <v>46272</v>
-      </c>
-      <c r="E8" s="6">
-        <v>46272</v>
-      </c>
-      <c r="F8" s="18">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G8" s="2">
-        <v>152.58000000000001</v>
-      </c>
-      <c r="H8" s="3">
-        <v>9.11</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="9"/>
-      <c r="X8" s="6">
-        <f t="shared" si="1"/>
-        <v>46239</v>
-      </c>
-      <c r="Y8" s="3">
-        <f t="shared" si="2"/>
-        <v>9.32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="6">
-        <v>46086</v>
-      </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="13"/>
-      <c r="X9" s="6">
-        <f t="shared" si="1"/>
-        <v>46272</v>
-      </c>
-      <c r="Y9" s="3">
-        <f t="shared" si="2"/>
-        <v>161.69</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" s="6">
-        <v>46098</v>
-      </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="13"/>
-      <c r="X10" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y10" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <v>46272</v>
-      </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G11" s="3"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="13"/>
-      <c r="X11" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y11" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" s="18" t="str">
-        <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v/>
-      </c>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G12" s="3"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="13"/>
-      <c r="X12" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y12" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A13" s="5"/>
-      <c r="B13" s="3"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="13"/>
-      <c r="N13" s="15"/>
-      <c r="X13" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y13" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="19"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="13"/>
-      <c r="X14" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" s="10"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="17"/>
-      <c r="L15" s="17"/>
-      <c r="M15" s="17"/>
-      <c r="N15" s="17"/>
-      <c r="O15" s="17"/>
-      <c r="P15" s="17"/>
-      <c r="Q15" s="17"/>
-      <c r="X15" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y15" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" s="3">
-        <v>200.38</v>
-      </c>
-      <c r="D16" s="10"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="13"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="20"/>
-      <c r="O16" s="21"/>
-      <c r="P16" s="13"/>
-      <c r="Q16" s="13"/>
-      <c r="X16" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y16" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D17" s="10"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="13"/>
-      <c r="X17" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y17" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D18" s="10"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="13"/>
-      <c r="X18" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y18" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D19" s="10"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="13"/>
-      <c r="X19" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y19" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D20" s="10"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="13"/>
-      <c r="X20" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y20" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D21" s="10"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="13"/>
-      <c r="X21" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y21" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D22" s="10"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="13"/>
-      <c r="X22" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y22" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D23" s="10"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="13"/>
-      <c r="X23" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y23" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D24" s="10"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="13"/>
-      <c r="X24" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y24" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D25" s="10"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="13"/>
-      <c r="X25" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y25" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D26" s="10"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="13"/>
-      <c r="X26" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y26" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D27" s="10"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="13"/>
-      <c r="X27" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y27" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D28" s="10"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="13"/>
-      <c r="X28" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y28" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D29" s="10"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="13"/>
-      <c r="X29" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y29" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D30" s="10"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="13"/>
-      <c r="X30" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y30" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D31" s="10"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="13"/>
-      <c r="X31" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y31" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D32" s="10"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="13"/>
-      <c r="X32" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y32" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D33" s="10"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="13"/>
-      <c r="X33" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y33" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D34" s="10"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="13"/>
-      <c r="X34" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y34" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D35" s="10"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="13"/>
-      <c r="X35" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y35" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D36" s="10"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="13"/>
-      <c r="X36" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y36" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D37" s="10"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
-      <c r="J37" s="13"/>
-      <c r="X37" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y37" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D38" s="10"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="13"/>
-      <c r="X38" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y38" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D39" s="10"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
-      <c r="J39" s="13"/>
-      <c r="X39" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y39" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D40" s="10"/>
-      <c r="E40" s="6"/>
-      <c r="F40" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
-      <c r="J40" s="13"/>
-      <c r="X40" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y40" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D41" s="10"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
-      <c r="J41" s="13"/>
-      <c r="X41" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y41" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D42" s="10"/>
-      <c r="E42" s="6"/>
-      <c r="F42" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G42" s="2"/>
-      <c r="H42" s="2"/>
-      <c r="I42" s="2"/>
-      <c r="J42" s="13"/>
-      <c r="X42" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y42" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D43" s="10"/>
-      <c r="E43" s="6"/>
-      <c r="F43" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G43" s="2"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
-      <c r="J43" s="13"/>
-      <c r="X43" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y43" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D44" s="10"/>
-      <c r="E44" s="6"/>
-      <c r="F44" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
-      <c r="I44" s="2"/>
-      <c r="J44" s="13"/>
-      <c r="X44" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y44" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D45" s="10"/>
-      <c r="E45" s="6"/>
-      <c r="F45" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
-      <c r="J45" s="13"/>
-      <c r="X45" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y45" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D46" s="10"/>
-      <c r="E46" s="6"/>
-      <c r="F46" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
-      <c r="J46" s="13"/>
-      <c r="X46" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y46" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D47" s="10"/>
-      <c r="E47" s="6"/>
-      <c r="F47" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="2"/>
-      <c r="J47" s="13"/>
-      <c r="X47" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y47" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D48" s="10"/>
-      <c r="E48" s="6"/>
-      <c r="F48" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
-      <c r="J48" s="13"/>
-      <c r="X48" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y48" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D49" s="10"/>
-      <c r="E49" s="6"/>
-      <c r="F49" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="2"/>
-      <c r="J49" s="13"/>
-      <c r="X49" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y49" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D50" s="10"/>
-      <c r="E50" s="6"/>
-      <c r="F50" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
-      <c r="J50" s="13"/>
-      <c r="X50" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y50" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D51" s="10"/>
-      <c r="E51" s="6"/>
-      <c r="F51" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
-      <c r="J51" s="13"/>
-      <c r="X51" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y51" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D52" s="10"/>
-      <c r="E52" s="6"/>
-      <c r="F52" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
-      <c r="J52" s="9"/>
-      <c r="X52" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y52" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D53" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E53" s="14"/>
-      <c r="F53" s="3"/>
-      <c r="G53" s="3">
-        <f>SUM(G3:G52)</f>
-        <v>200.38</v>
-      </c>
-      <c r="H53" s="3">
-        <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>9.11</v>
-      </c>
-      <c r="I53" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="D1:F1"/>
-    <mergeCell ref="G1:I1"/>
-    <mergeCell ref="K1:Q1"/>
-    <mergeCell ref="X1:Z1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="31" priority="1">
-      <formula>$Z$3="+"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="30" priority="2">
-      <formula>$B$16=$K$3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P3">
-    <cfRule type="expression" dxfId="29" priority="7">
-      <formula>$Z$3="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z3">
-    <cfRule type="expression" dxfId="28" priority="8">
-      <formula>$Z$3="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
 </file>